--- a/Configs/技能skill.xlsx
+++ b/Configs/技能skill.xlsx
@@ -177,7 +177,7 @@
     <t>提升5%风伤</t>
   </si>
   <si>
-    <t>3~造成击退效果，5~击退后造成30%减速，持续10秒|8~造成巨额击退效果|10~附加受到伤害增加50%，持续5秒</t>
+    <t>3~造成击退效果|5~击退后造成30%减速，持续10秒|8~造成巨额击退效果|10~附加受到伤害增加50%，持续5秒</t>
   </si>
   <si>
     <t>Icon/black-hole-128</t>
@@ -195,7 +195,7 @@
     <t>召唤物持续时间+1秒</t>
   </si>
   <si>
-    <t>3~继承属性提升至50%，5~子弹效果变为追踪|8~子弹最多可以穿刺两个目标|10~额外召唤两个风影守卫</t>
+    <t>3~继承属性提升至50%|5~子弹效果变为追踪|8~子弹最多可以穿刺两个目标|10~额外召唤两个风影守卫</t>
   </si>
   <si>
     <t>Icon/alien-128</t>
@@ -402,7 +402,7 @@
     <t>60030|20010|70709|80001</t>
   </si>
   <si>
-    <t>40003|70301</t>
+    <t>40005|70301</t>
   </si>
   <si>
     <t>40010|70301</t>
@@ -5832,7 +5832,7 @@
         <v>60031</v>
       </c>
       <c r="O81">
-        <v>40003</v>
+        <v>40005</v>
       </c>
       <c r="P81" t="s">
         <v>74</v>
@@ -5884,7 +5884,7 @@
         <v>60032</v>
       </c>
       <c r="O82">
-        <v>40003</v>
+        <v>40005</v>
       </c>
       <c r="P82" t="s">
         <v>74</v>

--- a/Configs/技能skill.xlsx
+++ b/Configs/技能skill.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="145">
   <si>
     <t>id</t>
   </si>
@@ -442,6 +442,27 @@
   </si>
   <si>
     <t>60040|90010</t>
+  </si>
+  <si>
+    <t>过载弹 I</t>
+  </si>
+  <si>
+    <t>连射5枚过载弹，每颗造成20%火伤</t>
+  </si>
+  <si>
+    <t>过载弹 II</t>
+  </si>
+  <si>
+    <t>连射10枚过载弹，每颗造成20%火伤</t>
+  </si>
+  <si>
+    <t>过载弹 III</t>
+  </si>
+  <si>
+    <t>连射10枚过载弹，每颗造成20%火伤，命中后发生2次散射</t>
+  </si>
+  <si>
+    <t>203010|201002</t>
   </si>
 </sst>
 </file>
@@ -1055,9 +1076,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1413,242 +1439,242 @@
   <dimension ref="A1:G10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="2" width="9" style="2"/>
-    <col min="3" max="3" width="32.75" style="2" customWidth="1"/>
-    <col min="4" max="4" width="26" style="2" customWidth="1"/>
-    <col min="5" max="5" width="42.5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="26" style="2" customWidth="1"/>
-    <col min="7" max="7" width="12.875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="2"/>
+    <col min="1" max="2" width="9" style="3"/>
+    <col min="3" max="3" width="32.75" style="3" customWidth="1"/>
+    <col min="4" max="4" width="26" style="3" customWidth="1"/>
+    <col min="5" max="5" width="42.5" style="3" customWidth="1"/>
+    <col min="6" max="6" width="26" style="3" customWidth="1"/>
+    <col min="7" max="7" width="12.875" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" ht="40.5" spans="1:7">
-      <c r="A3" s="2">
+      <c r="A3" s="3">
         <v>1001</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" ht="54" spans="1:7">
-      <c r="A4" s="2">
+      <c r="A4" s="3">
         <v>1002</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5" ht="40.5" spans="1:7">
-      <c r="A5" s="2">
+      <c r="A5" s="3">
         <v>1003</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="6" ht="40.5" spans="1:7">
-      <c r="A6" s="2">
+      <c r="A6" s="3">
         <v>1004</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" ht="40.5" spans="1:7">
-      <c r="A7" s="2">
+      <c r="A7" s="3">
         <v>1005</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="8" ht="54" spans="1:7">
-      <c r="A8" s="2">
+      <c r="A8" s="3">
         <v>1006</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="3" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="9" ht="40.5" spans="1:7">
-      <c r="A9" s="2">
+      <c r="A9" s="3">
         <v>1007</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="3" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="10" ht="40.5" spans="1:7">
-      <c r="A10" s="2">
+      <c r="A10" s="3">
         <v>1008</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="3" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1661,5191 +1687,5328 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q101"/>
+  <dimension ref="A1:Q104"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="3" width="9" style="1"/>
+    <col min="4" max="4" width="12.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="30.625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="24.375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5" style="1" customWidth="1"/>
+    <col min="8" max="13" width="9" style="1"/>
+    <col min="14" max="16" width="16" style="1" customWidth="1"/>
+    <col min="17" max="17" width="12.625" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:17">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" ht="27" spans="1:17">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:17">
-      <c r="A3" s="1">
+      <c r="A3" s="2">
         <f t="shared" ref="A3:A66" si="0">B3*100+C3</f>
         <v>1000001</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="2">
         <v>10000</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>1</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="E3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>10000</v>
       </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
         <v>10</v>
       </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
+      <c r="K3" s="1">
+        <v>0</v>
+      </c>
+      <c r="L3" s="1">
         <v>1</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="1">
         <v>10</v>
       </c>
-      <c r="N3" t="s">
-        <v>74</v>
-      </c>
-      <c r="O3" t="s">
-        <v>74</v>
-      </c>
-      <c r="P3">
+      <c r="N3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P3" s="1">
         <v>204010</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="Q3" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:17">
-      <c r="A4" s="1">
+      <c r="A4" s="2">
         <f t="shared" si="0"/>
         <v>1000101</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="2">
         <v>10001</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>1</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F4" t="s">
-        <v>74</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="E4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>10000</v>
       </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
+      <c r="I4" s="1">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1">
         <v>10</v>
       </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
+      <c r="K4" s="1">
+        <v>0</v>
+      </c>
+      <c r="L4" s="1">
         <v>1</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="1">
         <v>50</v>
       </c>
-      <c r="N4" t="s">
-        <v>74</v>
-      </c>
-      <c r="O4" t="s">
-        <v>74</v>
-      </c>
-      <c r="P4" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q4" t="s">
+      <c r="N4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q4" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:17">
-      <c r="A5" s="1">
+      <c r="A5" s="2">
         <f t="shared" si="0"/>
         <v>1000201</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="2">
         <v>10002</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>1</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E5" t="s">
-        <v>74</v>
-      </c>
-      <c r="F5" t="s">
-        <v>74</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="E5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>10000</v>
       </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1">
         <v>10</v>
       </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
+      <c r="K5" s="1">
+        <v>0</v>
+      </c>
+      <c r="L5" s="1">
         <v>1</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="1">
         <v>50</v>
       </c>
-      <c r="N5" t="s">
-        <v>74</v>
-      </c>
-      <c r="O5" t="s">
-        <v>74</v>
-      </c>
-      <c r="P5" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q5" t="s">
+      <c r="N5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q5" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:17">
-      <c r="A6" s="1">
+      <c r="A6" s="2">
         <f t="shared" si="0"/>
         <v>1000202</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="2">
         <v>10002</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>2</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F6" t="s">
-        <v>74</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="F6" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>10000</v>
       </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
         <v>10</v>
       </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
         <v>1</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="1">
         <v>50</v>
       </c>
-      <c r="N6" t="s">
-        <v>74</v>
-      </c>
-      <c r="O6" t="s">
-        <v>74</v>
-      </c>
-      <c r="P6">
+      <c r="N6" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P6" s="1">
         <v>103000</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="Q6" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:17">
-      <c r="A7" s="1">
+      <c r="A7" s="2">
         <f t="shared" si="0"/>
         <v>1000203</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="2">
         <v>10002</v>
       </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="C7" s="1">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F7" t="s">
-        <v>74</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="F7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>10000</v>
       </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
         <v>10</v>
       </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
         <v>1</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="1">
         <v>50</v>
       </c>
-      <c r="N7" t="s">
-        <v>74</v>
-      </c>
-      <c r="O7" t="s">
-        <v>74</v>
-      </c>
-      <c r="P7" t="s">
+      <c r="N7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P7" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="Q7" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:17">
-      <c r="A8" s="1">
+      <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>1000301</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="2">
         <v>10003</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>1</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E8" t="s">
-        <v>74</v>
-      </c>
-      <c r="F8" t="s">
-        <v>74</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="E8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>10000</v>
       </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1">
         <v>10</v>
       </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
+      <c r="K8" s="1">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1">
         <v>1</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="1">
         <v>50</v>
       </c>
-      <c r="N8" t="s">
-        <v>74</v>
-      </c>
-      <c r="O8" t="s">
-        <v>74</v>
-      </c>
-      <c r="P8" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q8" t="s">
+      <c r="N8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q8" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:17">
-      <c r="A9" s="1">
+      <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>1000401</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="2">
         <v>10004</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>1</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>3000</v>
       </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1">
         <v>110001</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="1">
         <v>40003</v>
       </c>
-      <c r="P9" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q9" t="s">
+      <c r="P9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q9" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:17">
-      <c r="A10" s="1">
+      <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>2000001</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="1">
         <v>20000</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>1</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E10" t="s">
-        <v>74</v>
-      </c>
-      <c r="F10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="E10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>10000</v>
       </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
         <v>8</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>0.8</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="1">
         <v>201</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="1">
         <v>15</v>
       </c>
-      <c r="N10" t="s">
-        <v>74</v>
-      </c>
-      <c r="O10" t="s">
-        <v>74</v>
-      </c>
-      <c r="P10" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q10" t="s">
+      <c r="N10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q10" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:17">
-      <c r="A11" s="1">
+      <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>1006101</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="2">
         <v>10061</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>1</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E11" t="s">
-        <v>74</v>
-      </c>
-      <c r="F11" t="s">
-        <v>74</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="E11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>3000</v>
       </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
         <v>10</v>
       </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
+      <c r="K11" s="1">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1">
         <v>1</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="1">
         <v>50</v>
       </c>
-      <c r="N11" t="s">
-        <v>74</v>
-      </c>
-      <c r="O11" t="s">
-        <v>74</v>
-      </c>
-      <c r="P11">
+      <c r="N11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P11" s="1">
         <v>201003</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="Q11" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:17">
-      <c r="A12" s="1">
+      <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>1006102</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="2">
         <v>10061</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="1">
         <v>2</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E12" t="s">
-        <v>74</v>
-      </c>
-      <c r="F12" t="s">
-        <v>74</v>
-      </c>
-      <c r="G12" t="s">
+      <c r="E12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>3000</v>
       </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
         <v>10</v>
       </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
+      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1">
         <v>1</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="1">
         <v>50</v>
       </c>
-      <c r="N12" t="s">
-        <v>74</v>
-      </c>
-      <c r="O12" t="s">
-        <v>74</v>
-      </c>
-      <c r="P12">
+      <c r="N12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P12" s="1">
         <v>201010</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="Q12" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:17">
-      <c r="A13" s="1">
+      <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>1006103</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="2">
         <v>10061</v>
       </c>
-      <c r="C13">
-        <v>3</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="C13" s="1">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F13" t="s">
-        <v>74</v>
-      </c>
-      <c r="G13" t="s">
+      <c r="E13" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>3000</v>
       </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1">
         <v>10</v>
       </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
+      <c r="K13" s="1">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1">
         <v>1</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="1">
         <v>50</v>
       </c>
-      <c r="N13" t="s">
-        <v>74</v>
-      </c>
-      <c r="O13" t="s">
-        <v>74</v>
-      </c>
-      <c r="P13" t="s">
+      <c r="N13" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P13" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="Q13" t="s">
+      <c r="Q13" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:17">
-      <c r="A14" s="1">
+      <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>100100</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="2">
         <v>1001</v>
       </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="C14" s="1">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E14" t="s">
-        <v>74</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="E14" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1">
         <v>1</v>
       </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
+      <c r="J14" s="1">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1">
         <v>101</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="1">
         <v>30</v>
       </c>
-      <c r="N14" t="s">
-        <v>74</v>
-      </c>
-      <c r="O14" t="s">
-        <v>74</v>
-      </c>
-      <c r="P14" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q14" t="s">
+      <c r="N14" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q14" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:17">
-      <c r="A15" s="1">
+      <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>100101</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="2">
         <f t="shared" ref="B15:B24" si="1">B14</f>
         <v>1001</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="1">
         <v>1</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E15" t="s">
-        <v>74</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="E15" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>10000</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="1">
         <v>1</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="1">
         <v>12</v>
       </c>
-      <c r="K15">
-        <v>3</v>
-      </c>
-      <c r="L15">
+      <c r="K15" s="1">
+        <v>3</v>
+      </c>
+      <c r="L15" s="1">
         <v>101</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="1">
         <v>30</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="1">
         <v>60001</v>
       </c>
-      <c r="O15" t="s">
-        <v>74</v>
-      </c>
-      <c r="P15" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q15" t="s">
+      <c r="O15" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q15" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:17">
-      <c r="A16" s="1">
+      <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>100102</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="2">
         <f t="shared" si="1"/>
         <v>1001</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="1">
         <v>2</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E16" t="s">
-        <v>74</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="E16" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>11000</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="1">
         <v>1</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="1">
         <v>12</v>
       </c>
-      <c r="K16">
-        <v>3</v>
-      </c>
-      <c r="L16">
+      <c r="K16" s="1">
+        <v>3</v>
+      </c>
+      <c r="L16" s="1">
         <v>101</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="1">
         <v>30</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="1">
         <v>60002</v>
       </c>
-      <c r="O16" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q16" t="s">
+      <c r="O16" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q16" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:17">
-      <c r="A17" s="1">
+      <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>100103</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="2">
         <f t="shared" si="1"/>
         <v>1001</v>
       </c>
-      <c r="C17">
-        <v>3</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="C17" s="1">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E17" t="s">
-        <v>74</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="E17" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <v>12000</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="1">
         <v>1</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="1">
         <v>12</v>
       </c>
-      <c r="K17">
-        <v>3</v>
-      </c>
-      <c r="L17">
+      <c r="K17" s="1">
+        <v>3</v>
+      </c>
+      <c r="L17" s="1">
         <v>101</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="1">
         <v>30</v>
       </c>
-      <c r="N17">
+      <c r="N17" s="1">
         <v>60003</v>
       </c>
-      <c r="O17" t="s">
-        <v>74</v>
-      </c>
-      <c r="P17">
+      <c r="O17" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P17" s="1">
         <v>201004</v>
       </c>
-      <c r="Q17" t="s">
+      <c r="Q17" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:17">
-      <c r="A18" s="1">
+      <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>100104</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="2">
         <f t="shared" si="1"/>
         <v>1001</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="1">
         <v>4</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E18" t="s">
-        <v>74</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="E18" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>13000</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="1">
         <v>1</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="1">
         <v>12</v>
       </c>
-      <c r="K18">
-        <v>3</v>
-      </c>
-      <c r="L18">
+      <c r="K18" s="1">
+        <v>3</v>
+      </c>
+      <c r="L18" s="1">
         <v>101</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="1">
         <v>30</v>
       </c>
-      <c r="N18">
+      <c r="N18" s="1">
         <v>60004</v>
       </c>
-      <c r="O18" t="s">
-        <v>74</v>
-      </c>
-      <c r="P18">
+      <c r="O18" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P18" s="1">
         <v>201004</v>
       </c>
-      <c r="Q18" t="s">
+      <c r="Q18" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:17">
-      <c r="A19" s="1">
+      <c r="A19" s="2">
         <f t="shared" si="0"/>
         <v>100105</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="2">
         <f t="shared" si="1"/>
         <v>1001</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="1">
         <v>5</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E19" t="s">
-        <v>74</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="E19" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>14000</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="1">
         <v>1</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="1">
         <v>12</v>
       </c>
-      <c r="K19">
-        <v>3</v>
-      </c>
-      <c r="L19">
+      <c r="K19" s="1">
+        <v>3</v>
+      </c>
+      <c r="L19" s="1">
         <v>101</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="1">
         <v>30</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="1">
         <v>60005</v>
       </c>
-      <c r="O19" t="s">
-        <v>74</v>
-      </c>
-      <c r="P19">
+      <c r="O19" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P19" s="1">
         <v>201008</v>
       </c>
-      <c r="Q19" t="s">
+      <c r="Q19" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:17">
-      <c r="A20" s="1">
+      <c r="A20" s="2">
         <f t="shared" si="0"/>
         <v>100106</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="2">
         <f t="shared" si="1"/>
         <v>1001</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="1">
         <v>6</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E20" t="s">
-        <v>74</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="E20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>15000</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="1">
         <v>1</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="1">
         <v>12</v>
       </c>
-      <c r="K20">
-        <v>3</v>
-      </c>
-      <c r="L20">
+      <c r="K20" s="1">
+        <v>3</v>
+      </c>
+      <c r="L20" s="1">
         <v>101</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="1">
         <v>30</v>
       </c>
-      <c r="N20">
+      <c r="N20" s="1">
         <v>60006</v>
       </c>
-      <c r="O20" s="1"/>
-      <c r="P20">
+      <c r="O20" s="2"/>
+      <c r="P20" s="1">
         <v>201008</v>
       </c>
-      <c r="Q20" t="s">
+      <c r="Q20" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:17">
-      <c r="A21" s="1">
+      <c r="A21" s="2">
         <f t="shared" si="0"/>
         <v>100107</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" s="2">
         <f t="shared" si="1"/>
         <v>1001</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="1">
         <v>7</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E21" t="s">
-        <v>74</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="E21" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G21" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <v>16000</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="1">
         <v>1</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="1">
         <v>12</v>
       </c>
-      <c r="K21">
-        <v>3</v>
-      </c>
-      <c r="L21">
+      <c r="K21" s="1">
+        <v>3</v>
+      </c>
+      <c r="L21" s="1">
         <v>101</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="1">
         <v>30</v>
       </c>
-      <c r="N21">
+      <c r="N21" s="1">
         <v>60007</v>
       </c>
-      <c r="O21" s="1"/>
-      <c r="P21">
+      <c r="O21" s="2"/>
+      <c r="P21" s="1">
         <v>201008</v>
       </c>
-      <c r="Q21" t="s">
+      <c r="Q21" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:17">
-      <c r="A22" s="1">
+      <c r="A22" s="2">
         <f t="shared" si="0"/>
         <v>100108</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" s="2">
         <f t="shared" si="1"/>
         <v>1001</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="1">
         <v>8</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E22" t="s">
-        <v>74</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="E22" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G22" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="1">
         <v>17000</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="1">
         <v>1</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="1">
         <v>12</v>
       </c>
-      <c r="K22">
-        <v>3</v>
-      </c>
-      <c r="L22">
+      <c r="K22" s="1">
+        <v>3</v>
+      </c>
+      <c r="L22" s="1">
         <v>101</v>
       </c>
-      <c r="M22">
+      <c r="M22" s="1">
         <v>30</v>
       </c>
-      <c r="N22">
+      <c r="N22" s="1">
         <v>60008</v>
       </c>
-      <c r="O22" s="1">
+      <c r="O22" s="2">
         <v>70010</v>
       </c>
-      <c r="P22">
+      <c r="P22" s="1">
         <v>201008</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="Q22" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:17">
-      <c r="A23" s="1">
+      <c r="A23" s="2">
         <f t="shared" si="0"/>
         <v>100109</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" s="2">
         <f t="shared" si="1"/>
         <v>1001</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="1">
         <v>9</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E23" t="s">
-        <v>74</v>
-      </c>
-      <c r="F23" t="s">
+      <c r="E23" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="1">
         <v>18000</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="1">
         <v>1</v>
       </c>
-      <c r="J23">
+      <c r="J23" s="1">
         <v>12</v>
       </c>
-      <c r="K23">
-        <v>3</v>
-      </c>
-      <c r="L23">
+      <c r="K23" s="1">
+        <v>3</v>
+      </c>
+      <c r="L23" s="1">
         <v>101</v>
       </c>
-      <c r="M23">
+      <c r="M23" s="1">
         <v>30</v>
       </c>
-      <c r="N23">
+      <c r="N23" s="1">
         <v>60009</v>
       </c>
-      <c r="O23" s="1">
+      <c r="O23" s="2">
         <v>70010</v>
       </c>
-      <c r="P23">
+      <c r="P23" s="1">
         <v>201008</v>
       </c>
-      <c r="Q23" t="s">
+      <c r="Q23" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:17">
-      <c r="A24" s="1">
+      <c r="A24" s="2">
         <f t="shared" si="0"/>
         <v>100110</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" s="2">
         <f t="shared" si="1"/>
         <v>1001</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="1">
         <v>10</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E24" t="s">
-        <v>74</v>
-      </c>
-      <c r="F24" t="s">
+      <c r="E24" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G24" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="1">
         <v>19000</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="1">
         <v>1</v>
       </c>
-      <c r="J24">
+      <c r="J24" s="1">
         <v>12</v>
       </c>
-      <c r="K24">
-        <v>3</v>
-      </c>
-      <c r="L24">
+      <c r="K24" s="1">
+        <v>3</v>
+      </c>
+      <c r="L24" s="1">
         <v>101</v>
       </c>
-      <c r="M24">
+      <c r="M24" s="1">
         <v>30</v>
       </c>
-      <c r="N24">
+      <c r="N24" s="1">
         <v>60010</v>
       </c>
-      <c r="O24" s="1">
+      <c r="O24" s="2">
         <v>70010</v>
       </c>
-      <c r="P24" t="s">
+      <c r="P24" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="Q24">
+      <c r="Q24" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:17">
-      <c r="A25" s="1">
+      <c r="A25" s="2">
         <f t="shared" si="0"/>
         <v>100200</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25" s="2">
         <f>B14+1</f>
         <v>1002</v>
       </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="C25" s="1">
+        <v>0</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E25" t="s">
-        <v>74</v>
-      </c>
-      <c r="F25" t="s">
+      <c r="E25" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G25" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+      <c r="I25" s="1">
         <v>1</v>
       </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>3</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25" t="s">
-        <v>74</v>
-      </c>
-      <c r="O25" t="s">
-        <v>74</v>
-      </c>
-      <c r="P25" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q25" t="s">
+      <c r="J25" s="1">
+        <v>0</v>
+      </c>
+      <c r="K25" s="1">
+        <v>3</v>
+      </c>
+      <c r="L25" s="1">
+        <v>0</v>
+      </c>
+      <c r="M25" s="1">
+        <v>0</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q25" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="26" spans="1:17">
-      <c r="A26" s="1">
+      <c r="A26" s="2">
         <f t="shared" si="0"/>
         <v>100201</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26" s="2">
         <f t="shared" ref="B26:B35" si="2">B25</f>
         <v>1002</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="1">
         <v>1</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E26" t="s">
-        <v>74</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="E26" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G26" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" s="1">
         <v>1</v>
       </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>3</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
-      <c r="N26" t="s">
+      <c r="J26" s="1">
+        <v>0</v>
+      </c>
+      <c r="K26" s="1">
+        <v>3</v>
+      </c>
+      <c r="L26" s="1">
+        <v>0</v>
+      </c>
+      <c r="M26" s="1">
+        <v>0</v>
+      </c>
+      <c r="N26" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="Q26" t="s">
+      <c r="Q26" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:17">
-      <c r="A27" s="1">
+      <c r="A27" s="2">
         <f t="shared" si="0"/>
         <v>100202</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B27" s="2">
         <f t="shared" si="2"/>
         <v>1002</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="1">
         <v>2</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E27" t="s">
-        <v>74</v>
-      </c>
-      <c r="F27" t="s">
+      <c r="E27" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G27" t="s">
+      <c r="G27" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27">
+      <c r="H27" s="1">
+        <v>0</v>
+      </c>
+      <c r="I27" s="1">
         <v>1</v>
       </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>3</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27">
-        <v>0</v>
-      </c>
-      <c r="N27" t="s">
+      <c r="J27" s="1">
+        <v>0</v>
+      </c>
+      <c r="K27" s="1">
+        <v>3</v>
+      </c>
+      <c r="L27" s="1">
+        <v>0</v>
+      </c>
+      <c r="M27" s="1">
+        <v>0</v>
+      </c>
+      <c r="N27" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="Q27" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17">
-      <c r="A28" s="1">
+      <c r="Q27" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" ht="27" spans="1:17">
+      <c r="A28" s="2">
         <f t="shared" si="0"/>
         <v>100203</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B28" s="2">
         <f t="shared" si="2"/>
         <v>1002</v>
       </c>
-      <c r="C28">
-        <v>3</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="C28" s="1">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E28" t="s">
-        <v>74</v>
-      </c>
-      <c r="F28" t="s">
+      <c r="E28" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G28" t="s">
+      <c r="G28" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
+      <c r="H28" s="1">
+        <v>0</v>
+      </c>
+      <c r="I28" s="1">
         <v>1</v>
       </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>3</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>0</v>
-      </c>
-      <c r="N28" t="s">
+      <c r="J28" s="1">
+        <v>0</v>
+      </c>
+      <c r="K28" s="1">
+        <v>3</v>
+      </c>
+      <c r="L28" s="1">
+        <v>0</v>
+      </c>
+      <c r="M28" s="1">
+        <v>0</v>
+      </c>
+      <c r="N28" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="Q28" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17">
-      <c r="A29" s="1">
+      <c r="Q28" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29" ht="27" spans="1:17">
+      <c r="A29" s="2">
         <f t="shared" si="0"/>
         <v>100204</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29" s="2">
         <f t="shared" si="2"/>
         <v>1002</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="1">
         <v>4</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E29" t="s">
-        <v>74</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="E29" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G29" t="s">
+      <c r="G29" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29">
+      <c r="H29" s="1">
+        <v>0</v>
+      </c>
+      <c r="I29" s="1">
         <v>1</v>
       </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29">
-        <v>3</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
-        <v>0</v>
-      </c>
-      <c r="N29" t="s">
+      <c r="J29" s="1">
+        <v>0</v>
+      </c>
+      <c r="K29" s="1">
+        <v>3</v>
+      </c>
+      <c r="L29" s="1">
+        <v>0</v>
+      </c>
+      <c r="M29" s="1">
+        <v>0</v>
+      </c>
+      <c r="N29" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="Q29" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17">
-      <c r="A30" s="1">
+      <c r="Q29" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30" ht="27" spans="1:17">
+      <c r="A30" s="2">
         <f t="shared" si="0"/>
         <v>100205</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30" s="2">
         <f t="shared" si="2"/>
         <v>1002</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="1">
         <v>5</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E30" t="s">
-        <v>74</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="E30" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G30" t="s">
+      <c r="G30" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-      <c r="I30">
+      <c r="H30" s="1">
+        <v>0</v>
+      </c>
+      <c r="I30" s="1">
         <v>1</v>
       </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>3</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
-      <c r="N30" t="s">
+      <c r="J30" s="1">
+        <v>0</v>
+      </c>
+      <c r="K30" s="1">
+        <v>3</v>
+      </c>
+      <c r="L30" s="1">
+        <v>0</v>
+      </c>
+      <c r="M30" s="1">
+        <v>0</v>
+      </c>
+      <c r="N30" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="Q30" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17">
-      <c r="A31" s="1">
+      <c r="Q30" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31" ht="27" spans="1:17">
+      <c r="A31" s="2">
         <f t="shared" si="0"/>
         <v>100206</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B31" s="2">
         <f t="shared" si="2"/>
         <v>1002</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="1">
         <v>6</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E31" t="s">
-        <v>74</v>
-      </c>
-      <c r="F31" t="s">
+      <c r="E31" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G31" t="s">
+      <c r="G31" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H31">
-        <v>0</v>
-      </c>
-      <c r="I31">
+      <c r="H31" s="1">
+        <v>0</v>
+      </c>
+      <c r="I31" s="1">
         <v>1</v>
       </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <v>3</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>0</v>
-      </c>
-      <c r="N31" t="s">
+      <c r="J31" s="1">
+        <v>0</v>
+      </c>
+      <c r="K31" s="1">
+        <v>3</v>
+      </c>
+      <c r="L31" s="1">
+        <v>0</v>
+      </c>
+      <c r="M31" s="1">
+        <v>0</v>
+      </c>
+      <c r="N31" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="Q31" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17">
-      <c r="A32" s="1">
+      <c r="Q31" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32" ht="27" spans="1:17">
+      <c r="A32" s="2">
         <f t="shared" si="0"/>
         <v>100207</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32" s="2">
         <f t="shared" si="2"/>
         <v>1002</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="1">
         <v>7</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E32" t="s">
-        <v>74</v>
-      </c>
-      <c r="F32" t="s">
+      <c r="E32" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G32" t="s">
+      <c r="G32" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H32">
-        <v>0</v>
-      </c>
-      <c r="I32">
+      <c r="H32" s="1">
+        <v>0</v>
+      </c>
+      <c r="I32" s="1">
         <v>1</v>
       </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32">
-        <v>3</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32" t="s">
+      <c r="J32" s="1">
+        <v>0</v>
+      </c>
+      <c r="K32" s="1">
+        <v>3</v>
+      </c>
+      <c r="L32" s="1">
+        <v>0</v>
+      </c>
+      <c r="M32" s="1">
+        <v>0</v>
+      </c>
+      <c r="N32" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="Q32" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17">
-      <c r="A33" s="1">
+      <c r="Q32" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" ht="27" spans="1:17">
+      <c r="A33" s="2">
         <f t="shared" si="0"/>
         <v>100208</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33" s="2">
         <f t="shared" si="2"/>
         <v>1002</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="1">
         <v>8</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E33" t="s">
-        <v>74</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="E33" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G33" t="s">
+      <c r="G33" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H33">
-        <v>0</v>
-      </c>
-      <c r="I33">
+      <c r="H33" s="1">
+        <v>0</v>
+      </c>
+      <c r="I33" s="1">
         <v>1</v>
       </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
-      <c r="K33">
-        <v>3</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-      <c r="N33" t="s">
+      <c r="J33" s="1">
+        <v>0</v>
+      </c>
+      <c r="K33" s="1">
+        <v>3</v>
+      </c>
+      <c r="L33" s="1">
+        <v>0</v>
+      </c>
+      <c r="M33" s="1">
+        <v>0</v>
+      </c>
+      <c r="N33" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="Q33" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17">
-      <c r="A34" s="1">
+      <c r="Q33" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34" ht="27" spans="1:17">
+      <c r="A34" s="2">
         <f t="shared" si="0"/>
         <v>100209</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B34" s="2">
         <f t="shared" si="2"/>
         <v>1002</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="1">
         <v>9</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E34" t="s">
-        <v>74</v>
-      </c>
-      <c r="F34" t="s">
+      <c r="E34" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G34" t="s">
+      <c r="G34" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H34">
-        <v>0</v>
-      </c>
-      <c r="I34">
+      <c r="H34" s="1">
+        <v>0</v>
+      </c>
+      <c r="I34" s="1">
         <v>1</v>
       </c>
-      <c r="J34">
-        <v>0</v>
-      </c>
-      <c r="K34">
-        <v>3</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-      <c r="N34" t="s">
+      <c r="J34" s="1">
+        <v>0</v>
+      </c>
+      <c r="K34" s="1">
+        <v>3</v>
+      </c>
+      <c r="L34" s="1">
+        <v>0</v>
+      </c>
+      <c r="M34" s="1">
+        <v>0</v>
+      </c>
+      <c r="N34" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="Q34" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17">
-      <c r="A35" s="1">
+      <c r="Q34" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35" ht="27" spans="1:17">
+      <c r="A35" s="2">
         <f t="shared" si="0"/>
         <v>100210</v>
       </c>
-      <c r="B35" s="1">
+      <c r="B35" s="2">
         <f t="shared" si="2"/>
         <v>1002</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="1">
         <v>10</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E35" t="s">
-        <v>74</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="E35" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G35" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
-      <c r="I35">
+      <c r="H35" s="1">
+        <v>0</v>
+      </c>
+      <c r="I35" s="1">
         <v>1</v>
       </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35">
-        <v>3</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35">
-        <v>0</v>
-      </c>
-      <c r="N35" t="s">
+      <c r="J35" s="1">
+        <v>0</v>
+      </c>
+      <c r="K35" s="1">
+        <v>3</v>
+      </c>
+      <c r="L35" s="1">
+        <v>0</v>
+      </c>
+      <c r="M35" s="1">
+        <v>0</v>
+      </c>
+      <c r="N35" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="Q35" t="s">
+      <c r="Q35" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="36" spans="1:17">
-      <c r="A36" s="1">
+      <c r="A36" s="2">
         <f t="shared" si="0"/>
         <v>100300</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B36" s="2">
         <f>B25+1</f>
         <v>1003</v>
       </c>
-      <c r="C36">
-        <v>0</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="C36" s="1">
+        <v>0</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E36" t="s">
-        <v>74</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="E36" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G36" t="s">
+      <c r="G36" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H36">
-        <v>0</v>
-      </c>
-      <c r="I36">
+      <c r="H36" s="1">
+        <v>0</v>
+      </c>
+      <c r="I36" s="1">
         <v>2</v>
       </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36">
-        <v>3</v>
-      </c>
-      <c r="L36">
+      <c r="J36" s="1">
+        <v>0</v>
+      </c>
+      <c r="K36" s="1">
+        <v>3</v>
+      </c>
+      <c r="L36" s="1">
         <v>102</v>
       </c>
-      <c r="M36">
+      <c r="M36" s="1">
         <v>30</v>
       </c>
-      <c r="N36" t="s">
-        <v>74</v>
-      </c>
-      <c r="O36" t="s">
-        <v>74</v>
-      </c>
-      <c r="P36" t="s">
+      <c r="N36" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P36" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="37" spans="1:17">
-      <c r="A37" s="1">
+      <c r="A37" s="2">
         <f t="shared" si="0"/>
         <v>100301</v>
       </c>
-      <c r="B37" s="1">
+      <c r="B37" s="2">
         <f t="shared" ref="B37:B46" si="3">B36</f>
         <v>1003</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="1">
         <v>1</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E37" t="s">
-        <v>74</v>
-      </c>
-      <c r="F37" t="s">
+      <c r="E37" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G37" t="s">
+      <c r="G37" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H37">
+      <c r="H37" s="1">
         <v>10000</v>
       </c>
-      <c r="I37">
+      <c r="I37" s="1">
         <v>2</v>
       </c>
-      <c r="J37">
+      <c r="J37" s="1">
         <v>15</v>
       </c>
-      <c r="K37">
-        <v>3</v>
-      </c>
-      <c r="L37">
+      <c r="K37" s="1">
+        <v>3</v>
+      </c>
+      <c r="L37" s="1">
         <v>102</v>
       </c>
-      <c r="M37">
+      <c r="M37" s="1">
         <v>30</v>
       </c>
-      <c r="N37">
+      <c r="N37" s="1">
         <v>60011</v>
       </c>
-      <c r="O37" s="1">
+      <c r="O37" s="2">
         <v>70201</v>
       </c>
-      <c r="P37" t="s">
+      <c r="P37" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:17">
-      <c r="A38" s="1">
+      <c r="A38" s="2">
         <f t="shared" si="0"/>
         <v>100302</v>
       </c>
-      <c r="B38" s="1">
+      <c r="B38" s="2">
         <f t="shared" si="3"/>
         <v>1003</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="1">
         <v>2</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E38" t="s">
-        <v>74</v>
-      </c>
-      <c r="F38" t="s">
+      <c r="E38" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G38" t="s">
+      <c r="G38" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H38">
+      <c r="H38" s="1">
         <v>11000</v>
       </c>
-      <c r="I38">
+      <c r="I38" s="1">
         <v>2</v>
       </c>
-      <c r="J38">
+      <c r="J38" s="1">
         <v>15</v>
       </c>
-      <c r="K38">
-        <v>3</v>
-      </c>
-      <c r="L38">
+      <c r="K38" s="1">
+        <v>3</v>
+      </c>
+      <c r="L38" s="1">
         <v>102</v>
       </c>
-      <c r="M38">
+      <c r="M38" s="1">
         <v>30</v>
       </c>
-      <c r="N38">
+      <c r="N38" s="1">
         <v>60012</v>
       </c>
-      <c r="O38" s="1">
+      <c r="O38" s="2">
         <v>70201</v>
       </c>
     </row>
     <row r="39" spans="1:17">
-      <c r="A39" s="1">
+      <c r="A39" s="2">
         <f t="shared" si="0"/>
         <v>100303</v>
       </c>
-      <c r="B39" s="1">
+      <c r="B39" s="2">
         <f t="shared" si="3"/>
         <v>1003</v>
       </c>
-      <c r="C39">
-        <v>3</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="C39" s="1">
+        <v>3</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E39" t="s">
-        <v>74</v>
-      </c>
-      <c r="F39" t="s">
+      <c r="E39" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G39" t="s">
+      <c r="G39" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H39">
+      <c r="H39" s="1">
         <v>12000</v>
       </c>
-      <c r="I39">
+      <c r="I39" s="1">
         <v>2</v>
       </c>
-      <c r="J39">
+      <c r="J39" s="1">
         <v>15</v>
       </c>
-      <c r="K39">
-        <v>3</v>
-      </c>
-      <c r="L39">
+      <c r="K39" s="1">
+        <v>3</v>
+      </c>
+      <c r="L39" s="1">
         <v>102</v>
       </c>
-      <c r="M39">
+      <c r="M39" s="1">
         <v>30</v>
       </c>
-      <c r="N39">
+      <c r="N39" s="1">
         <v>60013</v>
       </c>
-      <c r="O39" s="1">
+      <c r="O39" s="2">
         <v>70201</v>
       </c>
-      <c r="P39">
+      <c r="P39" s="1">
         <v>201005</v>
       </c>
     </row>
     <row r="40" spans="1:17">
-      <c r="A40" s="1">
+      <c r="A40" s="2">
         <f t="shared" si="0"/>
         <v>100304</v>
       </c>
-      <c r="B40" s="1">
+      <c r="B40" s="2">
         <f t="shared" si="3"/>
         <v>1003</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="1">
         <v>4</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E40" t="s">
-        <v>74</v>
-      </c>
-      <c r="F40" t="s">
+      <c r="E40" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F40" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G40" t="s">
+      <c r="G40" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H40">
+      <c r="H40" s="1">
         <v>13000</v>
       </c>
-      <c r="I40">
+      <c r="I40" s="1">
         <v>2</v>
       </c>
-      <c r="J40">
+      <c r="J40" s="1">
         <v>15</v>
       </c>
-      <c r="K40">
-        <v>3</v>
-      </c>
-      <c r="L40">
+      <c r="K40" s="1">
+        <v>3</v>
+      </c>
+      <c r="L40" s="1">
         <v>102</v>
       </c>
-      <c r="M40">
+      <c r="M40" s="1">
         <v>30</v>
       </c>
-      <c r="N40">
+      <c r="N40" s="1">
         <v>60014</v>
       </c>
-      <c r="O40" s="1">
+      <c r="O40" s="2">
         <v>70201</v>
       </c>
-      <c r="P40">
+      <c r="P40" s="1">
         <v>201005</v>
       </c>
     </row>
     <row r="41" spans="1:17">
-      <c r="A41" s="1">
+      <c r="A41" s="2">
         <f t="shared" si="0"/>
         <v>100305</v>
       </c>
-      <c r="B41" s="1">
+      <c r="B41" s="2">
         <f t="shared" si="3"/>
         <v>1003</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="1">
         <v>5</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E41" t="s">
-        <v>74</v>
-      </c>
-      <c r="F41" t="s">
+      <c r="E41" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G41" t="s">
+      <c r="G41" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H41">
+      <c r="H41" s="1">
         <v>14000</v>
       </c>
-      <c r="I41">
+      <c r="I41" s="1">
         <v>2</v>
       </c>
-      <c r="J41">
+      <c r="J41" s="1">
         <v>15</v>
       </c>
-      <c r="K41">
-        <v>3</v>
-      </c>
-      <c r="L41">
+      <c r="K41" s="1">
+        <v>3</v>
+      </c>
+      <c r="L41" s="1">
         <v>102</v>
       </c>
-      <c r="M41">
+      <c r="M41" s="1">
         <v>30</v>
       </c>
-      <c r="N41">
+      <c r="N41" s="1">
         <v>60015</v>
       </c>
-      <c r="O41" s="1">
+      <c r="O41" s="2">
         <v>70204</v>
       </c>
-      <c r="P41">
+      <c r="P41" s="1">
         <v>201005</v>
       </c>
     </row>
     <row r="42" spans="1:17">
-      <c r="A42" s="1">
+      <c r="A42" s="2">
         <f t="shared" si="0"/>
         <v>100306</v>
       </c>
-      <c r="B42" s="1">
+      <c r="B42" s="2">
         <f t="shared" si="3"/>
         <v>1003</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="1">
         <v>6</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E42" t="s">
-        <v>74</v>
-      </c>
-      <c r="F42" t="s">
+      <c r="E42" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G42" t="s">
+      <c r="G42" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H42">
+      <c r="H42" s="1">
         <v>15000</v>
       </c>
-      <c r="I42">
+      <c r="I42" s="1">
         <v>2</v>
       </c>
-      <c r="J42">
+      <c r="J42" s="1">
         <v>15</v>
       </c>
-      <c r="K42">
-        <v>3</v>
-      </c>
-      <c r="L42">
+      <c r="K42" s="1">
+        <v>3</v>
+      </c>
+      <c r="L42" s="1">
         <v>102</v>
       </c>
-      <c r="M42">
+      <c r="M42" s="1">
         <v>30</v>
       </c>
-      <c r="N42">
+      <c r="N42" s="1">
         <v>60016</v>
       </c>
-      <c r="O42" s="1">
+      <c r="O42" s="2">
         <v>70204</v>
       </c>
-      <c r="P42">
+      <c r="P42" s="1">
         <v>201005</v>
       </c>
     </row>
     <row r="43" spans="1:17">
-      <c r="A43" s="1">
+      <c r="A43" s="2">
         <f t="shared" si="0"/>
         <v>100307</v>
       </c>
-      <c r="B43" s="1">
+      <c r="B43" s="2">
         <f t="shared" si="3"/>
         <v>1003</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="1">
         <v>7</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E43" t="s">
-        <v>74</v>
-      </c>
-      <c r="F43" t="s">
+      <c r="E43" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G43" t="s">
+      <c r="G43" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H43">
+      <c r="H43" s="1">
         <v>16000</v>
       </c>
-      <c r="I43">
+      <c r="I43" s="1">
         <v>2</v>
       </c>
-      <c r="J43">
+      <c r="J43" s="1">
         <v>15</v>
       </c>
-      <c r="K43">
-        <v>3</v>
-      </c>
-      <c r="L43">
+      <c r="K43" s="1">
+        <v>3</v>
+      </c>
+      <c r="L43" s="1">
         <v>102</v>
       </c>
-      <c r="M43">
+      <c r="M43" s="1">
         <v>30</v>
       </c>
-      <c r="N43">
+      <c r="N43" s="1">
         <v>60017</v>
       </c>
-      <c r="O43" s="1">
+      <c r="O43" s="2">
         <v>70204</v>
       </c>
-      <c r="P43">
+      <c r="P43" s="1">
         <v>201005</v>
       </c>
     </row>
     <row r="44" spans="1:17">
-      <c r="A44" s="1">
+      <c r="A44" s="2">
         <f t="shared" si="0"/>
         <v>100308</v>
       </c>
-      <c r="B44" s="1">
+      <c r="B44" s="2">
         <f t="shared" si="3"/>
         <v>1003</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="1">
         <v>8</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E44" t="s">
-        <v>74</v>
-      </c>
-      <c r="F44" t="s">
+      <c r="E44" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F44" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G44" t="s">
+      <c r="G44" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H44">
+      <c r="H44" s="1">
         <v>17000</v>
       </c>
-      <c r="I44">
+      <c r="I44" s="1">
         <v>2</v>
       </c>
-      <c r="J44">
+      <c r="J44" s="1">
         <v>15</v>
       </c>
-      <c r="K44">
-        <v>3</v>
-      </c>
-      <c r="L44">
+      <c r="K44" s="1">
+        <v>3</v>
+      </c>
+      <c r="L44" s="1">
         <v>102</v>
       </c>
-      <c r="M44">
+      <c r="M44" s="1">
         <v>30</v>
       </c>
-      <c r="N44">
+      <c r="N44" s="1">
         <v>60018</v>
       </c>
-      <c r="O44" s="1">
+      <c r="O44" s="2">
         <v>70204</v>
       </c>
-      <c r="P44" t="s">
+      <c r="P44" s="1" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:17">
-      <c r="A45" s="1">
+      <c r="A45" s="2">
         <f t="shared" si="0"/>
         <v>100309</v>
       </c>
-      <c r="B45" s="1">
+      <c r="B45" s="2">
         <f t="shared" si="3"/>
         <v>1003</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="1">
         <v>9</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E45" t="s">
-        <v>74</v>
-      </c>
-      <c r="F45" t="s">
+      <c r="E45" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F45" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G45" t="s">
+      <c r="G45" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H45">
+      <c r="H45" s="1">
         <v>18000</v>
       </c>
-      <c r="I45">
+      <c r="I45" s="1">
         <v>2</v>
       </c>
-      <c r="J45">
+      <c r="J45" s="1">
         <v>15</v>
       </c>
-      <c r="K45">
-        <v>3</v>
-      </c>
-      <c r="L45">
+      <c r="K45" s="1">
+        <v>3</v>
+      </c>
+      <c r="L45" s="1">
         <v>102</v>
       </c>
-      <c r="M45">
+      <c r="M45" s="1">
         <v>30</v>
       </c>
-      <c r="N45">
+      <c r="N45" s="1">
         <v>60019</v>
       </c>
-      <c r="O45" s="1">
+      <c r="O45" s="2">
         <v>70204</v>
       </c>
-      <c r="P45" t="s">
+      <c r="P45" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:17">
-      <c r="A46" s="1">
+    <row r="46" ht="27" spans="1:17">
+      <c r="A46" s="2">
         <f t="shared" si="0"/>
         <v>100310</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B46" s="2">
         <f t="shared" si="3"/>
         <v>1003</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="1">
         <v>10</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E46" t="s">
-        <v>74</v>
-      </c>
-      <c r="F46" t="s">
+      <c r="E46" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F46" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G46" t="s">
+      <c r="G46" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H46">
+      <c r="H46" s="1">
         <v>19000</v>
       </c>
-      <c r="I46">
+      <c r="I46" s="1">
         <v>2</v>
       </c>
-      <c r="J46">
+      <c r="J46" s="1">
         <v>15</v>
       </c>
-      <c r="K46">
-        <v>3</v>
-      </c>
-      <c r="L46">
+      <c r="K46" s="1">
+        <v>3</v>
+      </c>
+      <c r="L46" s="1">
         <v>102</v>
       </c>
-      <c r="M46">
+      <c r="M46" s="1">
         <v>30</v>
       </c>
-      <c r="N46">
+      <c r="N46" s="1">
         <v>60020</v>
       </c>
-      <c r="O46" s="1">
+      <c r="O46" s="2">
         <v>70214</v>
       </c>
-      <c r="P46" t="s">
+      <c r="P46" s="1" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:17">
-      <c r="A47" s="1">
+      <c r="A47" s="2">
         <f t="shared" si="0"/>
         <v>100400</v>
       </c>
-      <c r="B47" s="1">
+      <c r="B47" s="2">
         <f>B36+1</f>
         <v>1004</v>
       </c>
-      <c r="C47">
-        <v>0</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="C47" s="1">
+        <v>0</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E47" t="s">
-        <v>74</v>
-      </c>
-      <c r="F47" t="s">
+      <c r="E47" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F47" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G47" t="s">
+      <c r="G47" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H47">
-        <v>0</v>
-      </c>
-      <c r="I47">
+      <c r="H47" s="1">
+        <v>0</v>
+      </c>
+      <c r="I47" s="1">
         <v>2</v>
       </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47">
-        <v>3</v>
-      </c>
-      <c r="L47">
-        <v>0</v>
-      </c>
-      <c r="M47">
-        <v>0</v>
-      </c>
-      <c r="N47" t="s">
-        <v>74</v>
-      </c>
-      <c r="O47" t="s">
-        <v>74</v>
-      </c>
-      <c r="P47" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17">
-      <c r="A48" s="1">
+      <c r="J47" s="1">
+        <v>0</v>
+      </c>
+      <c r="K47" s="1">
+        <v>3</v>
+      </c>
+      <c r="L47" s="1">
+        <v>0</v>
+      </c>
+      <c r="M47" s="1">
+        <v>0</v>
+      </c>
+      <c r="N47" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O47" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P47" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="48" ht="27" spans="1:17">
+      <c r="A48" s="2">
         <f t="shared" si="0"/>
         <v>100401</v>
       </c>
-      <c r="B48" s="1">
+      <c r="B48" s="2">
         <f t="shared" ref="B48:B57" si="4">B47</f>
         <v>1004</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="1">
         <v>1</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E48" t="s">
-        <v>74</v>
-      </c>
-      <c r="F48" t="s">
+      <c r="E48" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F48" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G48" t="s">
+      <c r="G48" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
-      <c r="I48">
+      <c r="H48" s="1">
+        <v>0</v>
+      </c>
+      <c r="I48" s="1">
         <v>2</v>
       </c>
-      <c r="J48">
-        <v>0</v>
-      </c>
-      <c r="K48">
-        <v>3</v>
-      </c>
-      <c r="L48">
-        <v>0</v>
-      </c>
-      <c r="M48">
-        <v>0</v>
-      </c>
-      <c r="N48" t="s">
+      <c r="J48" s="1">
+        <v>0</v>
+      </c>
+      <c r="K48" s="1">
+        <v>3</v>
+      </c>
+      <c r="L48" s="1">
+        <v>0</v>
+      </c>
+      <c r="M48" s="1">
+        <v>0</v>
+      </c>
+      <c r="N48" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="P48" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16">
-      <c r="A49" s="1">
+      <c r="P48" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49" ht="27" spans="1:16">
+      <c r="A49" s="2">
         <f t="shared" si="0"/>
         <v>100402</v>
       </c>
-      <c r="B49" s="1">
+      <c r="B49" s="2">
         <f t="shared" si="4"/>
         <v>1004</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="1">
         <v>2</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E49" t="s">
-        <v>74</v>
-      </c>
-      <c r="F49" t="s">
+      <c r="E49" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F49" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G49" t="s">
+      <c r="G49" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H49">
-        <v>0</v>
-      </c>
-      <c r="I49">
+      <c r="H49" s="1">
+        <v>0</v>
+      </c>
+      <c r="I49" s="1">
         <v>2</v>
       </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>3</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-      <c r="M49">
-        <v>0</v>
-      </c>
-      <c r="N49" t="s">
+      <c r="J49" s="1">
+        <v>0</v>
+      </c>
+      <c r="K49" s="1">
+        <v>3</v>
+      </c>
+      <c r="L49" s="1">
+        <v>0</v>
+      </c>
+      <c r="M49" s="1">
+        <v>0</v>
+      </c>
+      <c r="N49" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="P49" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16">
-      <c r="A50" s="1">
+      <c r="P49" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="50" ht="27" spans="1:16">
+      <c r="A50" s="2">
         <f t="shared" si="0"/>
         <v>100403</v>
       </c>
-      <c r="B50" s="1">
+      <c r="B50" s="2">
         <f t="shared" si="4"/>
         <v>1004</v>
       </c>
-      <c r="C50">
-        <v>3</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="C50" s="1">
+        <v>3</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E50" t="s">
-        <v>74</v>
-      </c>
-      <c r="F50" t="s">
+      <c r="E50" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F50" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G50" t="s">
+      <c r="G50" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H50">
-        <v>0</v>
-      </c>
-      <c r="I50">
+      <c r="H50" s="1">
+        <v>0</v>
+      </c>
+      <c r="I50" s="1">
         <v>2</v>
       </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
-      <c r="K50">
-        <v>3</v>
-      </c>
-      <c r="L50">
-        <v>0</v>
-      </c>
-      <c r="M50">
-        <v>0</v>
-      </c>
-      <c r="N50" t="s">
+      <c r="J50" s="1">
+        <v>0</v>
+      </c>
+      <c r="K50" s="1">
+        <v>3</v>
+      </c>
+      <c r="L50" s="1">
+        <v>0</v>
+      </c>
+      <c r="M50" s="1">
+        <v>0</v>
+      </c>
+      <c r="N50" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="P50" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16">
-      <c r="A51" s="1">
+      <c r="P50" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="51" ht="27" spans="1:16">
+      <c r="A51" s="2">
         <f t="shared" si="0"/>
         <v>100404</v>
       </c>
-      <c r="B51" s="1">
+      <c r="B51" s="2">
         <f t="shared" si="4"/>
         <v>1004</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="1">
         <v>4</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D51" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E51" t="s">
-        <v>74</v>
-      </c>
-      <c r="F51" t="s">
+      <c r="E51" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F51" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G51" t="s">
+      <c r="G51" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H51">
-        <v>0</v>
-      </c>
-      <c r="I51">
+      <c r="H51" s="1">
+        <v>0</v>
+      </c>
+      <c r="I51" s="1">
         <v>2</v>
       </c>
-      <c r="J51">
-        <v>0</v>
-      </c>
-      <c r="K51">
-        <v>3</v>
-      </c>
-      <c r="L51">
-        <v>0</v>
-      </c>
-      <c r="M51">
-        <v>0</v>
-      </c>
-      <c r="N51" t="s">
+      <c r="J51" s="1">
+        <v>0</v>
+      </c>
+      <c r="K51" s="1">
+        <v>3</v>
+      </c>
+      <c r="L51" s="1">
+        <v>0</v>
+      </c>
+      <c r="M51" s="1">
+        <v>0</v>
+      </c>
+      <c r="N51" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="P51" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16">
-      <c r="A52" s="1">
+      <c r="P51" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="52" ht="27" spans="1:16">
+      <c r="A52" s="2">
         <f t="shared" si="0"/>
         <v>100405</v>
       </c>
-      <c r="B52" s="1">
+      <c r="B52" s="2">
         <f t="shared" si="4"/>
         <v>1004</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="1">
         <v>5</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D52" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E52" t="s">
-        <v>74</v>
-      </c>
-      <c r="F52" t="s">
+      <c r="E52" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F52" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G52" t="s">
+      <c r="G52" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H52">
-        <v>0</v>
-      </c>
-      <c r="I52">
+      <c r="H52" s="1">
+        <v>0</v>
+      </c>
+      <c r="I52" s="1">
         <v>2</v>
       </c>
-      <c r="J52">
-        <v>0</v>
-      </c>
-      <c r="K52">
-        <v>3</v>
-      </c>
-      <c r="L52">
-        <v>0</v>
-      </c>
-      <c r="M52">
-        <v>0</v>
-      </c>
-      <c r="N52" t="s">
+      <c r="J52" s="1">
+        <v>0</v>
+      </c>
+      <c r="K52" s="1">
+        <v>3</v>
+      </c>
+      <c r="L52" s="1">
+        <v>0</v>
+      </c>
+      <c r="M52" s="1">
+        <v>0</v>
+      </c>
+      <c r="N52" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="P52" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16">
-      <c r="A53" s="1">
+      <c r="P52" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="53" ht="27" spans="1:16">
+      <c r="A53" s="2">
         <f t="shared" si="0"/>
         <v>100406</v>
       </c>
-      <c r="B53" s="1">
+      <c r="B53" s="2">
         <f t="shared" si="4"/>
         <v>1004</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="1">
         <v>6</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D53" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E53" t="s">
-        <v>74</v>
-      </c>
-      <c r="F53" t="s">
+      <c r="E53" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F53" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G53" t="s">
+      <c r="G53" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H53">
-        <v>0</v>
-      </c>
-      <c r="I53">
+      <c r="H53" s="1">
+        <v>0</v>
+      </c>
+      <c r="I53" s="1">
         <v>2</v>
       </c>
-      <c r="J53">
-        <v>0</v>
-      </c>
-      <c r="K53">
-        <v>3</v>
-      </c>
-      <c r="L53">
-        <v>0</v>
-      </c>
-      <c r="M53">
-        <v>0</v>
-      </c>
-      <c r="N53" t="s">
+      <c r="J53" s="1">
+        <v>0</v>
+      </c>
+      <c r="K53" s="1">
+        <v>3</v>
+      </c>
+      <c r="L53" s="1">
+        <v>0</v>
+      </c>
+      <c r="M53" s="1">
+        <v>0</v>
+      </c>
+      <c r="N53" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="P53" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16">
-      <c r="A54" s="1">
+      <c r="P53" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="54" ht="27" spans="1:16">
+      <c r="A54" s="2">
         <f t="shared" si="0"/>
         <v>100407</v>
       </c>
-      <c r="B54" s="1">
+      <c r="B54" s="2">
         <f t="shared" si="4"/>
         <v>1004</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="1">
         <v>7</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D54" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E54" t="s">
-        <v>74</v>
-      </c>
-      <c r="F54" t="s">
+      <c r="E54" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F54" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G54" t="s">
+      <c r="G54" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H54">
-        <v>0</v>
-      </c>
-      <c r="I54">
+      <c r="H54" s="1">
+        <v>0</v>
+      </c>
+      <c r="I54" s="1">
         <v>2</v>
       </c>
-      <c r="J54">
-        <v>0</v>
-      </c>
-      <c r="K54">
-        <v>3</v>
-      </c>
-      <c r="L54">
-        <v>0</v>
-      </c>
-      <c r="M54">
-        <v>0</v>
-      </c>
-      <c r="N54" t="s">
+      <c r="J54" s="1">
+        <v>0</v>
+      </c>
+      <c r="K54" s="1">
+        <v>3</v>
+      </c>
+      <c r="L54" s="1">
+        <v>0</v>
+      </c>
+      <c r="M54" s="1">
+        <v>0</v>
+      </c>
+      <c r="N54" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="P54" t="s">
+      <c r="P54" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="55" spans="1:16">
-      <c r="A55" s="1">
+      <c r="A55" s="2">
         <f t="shared" si="0"/>
         <v>100408</v>
       </c>
-      <c r="B55" s="1">
+      <c r="B55" s="2">
         <f t="shared" si="4"/>
         <v>1004</v>
       </c>
-      <c r="C55">
+      <c r="C55" s="1">
         <v>8</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D55" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E55" t="s">
-        <v>74</v>
-      </c>
-      <c r="F55" t="s">
+      <c r="E55" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F55" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G55" t="s">
+      <c r="G55" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H55">
-        <v>0</v>
-      </c>
-      <c r="I55">
+      <c r="H55" s="1">
+        <v>0</v>
+      </c>
+      <c r="I55" s="1">
         <v>2</v>
       </c>
-      <c r="J55">
-        <v>0</v>
-      </c>
-      <c r="K55">
-        <v>3</v>
-      </c>
-      <c r="L55">
-        <v>0</v>
-      </c>
-      <c r="M55">
-        <v>0</v>
-      </c>
-      <c r="N55" t="s">
+      <c r="J55" s="1">
+        <v>0</v>
+      </c>
+      <c r="K55" s="1">
+        <v>3</v>
+      </c>
+      <c r="L55" s="1">
+        <v>0</v>
+      </c>
+      <c r="M55" s="1">
+        <v>0</v>
+      </c>
+      <c r="N55" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="P55" t="s">
+      <c r="P55" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="56" spans="1:16">
-      <c r="A56" s="1">
+      <c r="A56" s="2">
         <f t="shared" si="0"/>
         <v>100409</v>
       </c>
-      <c r="B56" s="1">
+      <c r="B56" s="2">
         <f t="shared" si="4"/>
         <v>1004</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="1">
         <v>9</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D56" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E56" t="s">
-        <v>74</v>
-      </c>
-      <c r="F56" t="s">
+      <c r="E56" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F56" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G56" t="s">
+      <c r="G56" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H56">
-        <v>0</v>
-      </c>
-      <c r="I56">
+      <c r="H56" s="1">
+        <v>0</v>
+      </c>
+      <c r="I56" s="1">
         <v>2</v>
       </c>
-      <c r="J56">
-        <v>0</v>
-      </c>
-      <c r="K56">
-        <v>3</v>
-      </c>
-      <c r="L56">
-        <v>0</v>
-      </c>
-      <c r="M56">
-        <v>0</v>
-      </c>
-      <c r="N56" t="s">
+      <c r="J56" s="1">
+        <v>0</v>
+      </c>
+      <c r="K56" s="1">
+        <v>3</v>
+      </c>
+      <c r="L56" s="1">
+        <v>0</v>
+      </c>
+      <c r="M56" s="1">
+        <v>0</v>
+      </c>
+      <c r="N56" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="P56" t="s">
+      <c r="P56" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="57" spans="1:16">
-      <c r="A57" s="1">
+      <c r="A57" s="2">
         <f t="shared" si="0"/>
         <v>100410</v>
       </c>
-      <c r="B57" s="1">
+      <c r="B57" s="2">
         <f t="shared" si="4"/>
         <v>1004</v>
       </c>
-      <c r="C57">
+      <c r="C57" s="1">
         <v>10</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D57" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E57" t="s">
-        <v>74</v>
-      </c>
-      <c r="F57" t="s">
+      <c r="E57" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F57" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G57" t="s">
+      <c r="G57" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H57">
-        <v>0</v>
-      </c>
-      <c r="I57">
+      <c r="H57" s="1">
+        <v>0</v>
+      </c>
+      <c r="I57" s="1">
         <v>2</v>
       </c>
-      <c r="J57">
-        <v>0</v>
-      </c>
-      <c r="K57">
-        <v>3</v>
-      </c>
-      <c r="L57">
-        <v>0</v>
-      </c>
-      <c r="M57">
-        <v>0</v>
-      </c>
-      <c r="N57" t="s">
+      <c r="J57" s="1">
+        <v>0</v>
+      </c>
+      <c r="K57" s="1">
+        <v>3</v>
+      </c>
+      <c r="L57" s="1">
+        <v>0</v>
+      </c>
+      <c r="M57" s="1">
+        <v>0</v>
+      </c>
+      <c r="N57" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="P57" t="s">
+      <c r="P57" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="58" spans="1:16">
-      <c r="A58" s="1">
+      <c r="A58" s="2">
         <f t="shared" si="0"/>
         <v>100500</v>
       </c>
-      <c r="B58" s="1">
+      <c r="B58" s="2">
         <f>B47+1</f>
         <v>1005</v>
       </c>
-      <c r="C58">
-        <v>0</v>
-      </c>
-      <c r="D58" t="s">
+      <c r="C58" s="1">
+        <v>0</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E58" t="s">
-        <v>74</v>
-      </c>
-      <c r="F58" t="s">
+      <c r="E58" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F58" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G58" t="s">
+      <c r="G58" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H58">
-        <v>0</v>
-      </c>
-      <c r="I58">
-        <v>3</v>
-      </c>
-      <c r="J58">
-        <v>0</v>
-      </c>
-      <c r="K58">
-        <v>3</v>
-      </c>
-      <c r="L58">
+      <c r="H58" s="1">
+        <v>0</v>
+      </c>
+      <c r="I58" s="1">
+        <v>3</v>
+      </c>
+      <c r="J58" s="1">
+        <v>0</v>
+      </c>
+      <c r="K58" s="1">
+        <v>3</v>
+      </c>
+      <c r="L58" s="1">
         <v>103</v>
       </c>
-      <c r="M58">
+      <c r="M58" s="1">
         <v>30</v>
       </c>
-      <c r="N58" t="s">
-        <v>74</v>
-      </c>
-      <c r="O58" t="s">
-        <v>74</v>
-      </c>
-      <c r="P58" t="s">
+      <c r="N58" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O58" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P58" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="59" spans="1:16">
-      <c r="A59" s="1">
+      <c r="A59" s="2">
         <f t="shared" si="0"/>
         <v>100501</v>
       </c>
-      <c r="B59" s="1">
+      <c r="B59" s="2">
         <f t="shared" ref="B59:B68" si="5">B58</f>
         <v>1005</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="1">
         <v>1</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D59" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E59" t="s">
-        <v>74</v>
-      </c>
-      <c r="F59" t="s">
+      <c r="E59" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G59" t="s">
+      <c r="G59" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H59">
+      <c r="H59" s="1">
         <v>1000</v>
       </c>
-      <c r="I59">
-        <v>3</v>
-      </c>
-      <c r="J59">
+      <c r="I59" s="1">
+        <v>3</v>
+      </c>
+      <c r="J59" s="1">
         <v>20</v>
       </c>
-      <c r="K59">
-        <v>3</v>
-      </c>
-      <c r="L59">
+      <c r="K59" s="1">
+        <v>3</v>
+      </c>
+      <c r="L59" s="1">
         <v>103</v>
       </c>
-      <c r="M59">
+      <c r="M59" s="1">
         <v>30</v>
       </c>
-      <c r="N59">
+      <c r="N59" s="1">
         <v>60021</v>
       </c>
-      <c r="O59" t="s">
-        <v>74</v>
-      </c>
-      <c r="P59">
+      <c r="O59" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P59" s="1">
         <v>202001</v>
       </c>
     </row>
     <row r="60" spans="1:16">
-      <c r="A60" s="1">
+      <c r="A60" s="2">
         <f t="shared" si="0"/>
         <v>100502</v>
       </c>
-      <c r="B60" s="1">
+      <c r="B60" s="2">
         <f t="shared" si="5"/>
         <v>1005</v>
       </c>
-      <c r="C60">
+      <c r="C60" s="1">
         <v>2</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D60" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E60" t="s">
-        <v>74</v>
-      </c>
-      <c r="F60" t="s">
+      <c r="E60" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F60" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G60" t="s">
+      <c r="G60" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H60">
+      <c r="H60" s="1">
         <v>2000</v>
       </c>
-      <c r="I60">
-        <v>3</v>
-      </c>
-      <c r="J60">
+      <c r="I60" s="1">
+        <v>3</v>
+      </c>
+      <c r="J60" s="1">
         <v>20</v>
       </c>
-      <c r="K60">
-        <v>3</v>
-      </c>
-      <c r="L60">
+      <c r="K60" s="1">
+        <v>3</v>
+      </c>
+      <c r="L60" s="1">
         <v>103</v>
       </c>
-      <c r="M60">
+      <c r="M60" s="1">
         <v>30</v>
       </c>
-      <c r="N60">
+      <c r="N60" s="1">
         <v>60022</v>
       </c>
-      <c r="O60" t="s">
-        <v>74</v>
-      </c>
-      <c r="P60">
+      <c r="O60" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P60" s="1">
         <v>202001</v>
       </c>
     </row>
     <row r="61" spans="1:16">
-      <c r="A61" s="1">
+      <c r="A61" s="2">
         <f t="shared" si="0"/>
         <v>100503</v>
       </c>
-      <c r="B61" s="1">
+      <c r="B61" s="2">
         <f t="shared" si="5"/>
         <v>1005</v>
       </c>
-      <c r="C61">
-        <v>3</v>
-      </c>
-      <c r="D61" t="s">
+      <c r="C61" s="1">
+        <v>3</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E61" t="s">
-        <v>74</v>
-      </c>
-      <c r="F61" t="s">
+      <c r="E61" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G61" t="s">
+      <c r="G61" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H61">
+      <c r="H61" s="1">
         <v>3000</v>
       </c>
-      <c r="I61">
-        <v>3</v>
-      </c>
-      <c r="J61">
+      <c r="I61" s="1">
+        <v>3</v>
+      </c>
+      <c r="J61" s="1">
         <v>20</v>
       </c>
-      <c r="K61">
-        <v>3</v>
-      </c>
-      <c r="L61">
+      <c r="K61" s="1">
+        <v>3</v>
+      </c>
+      <c r="L61" s="1">
         <v>103</v>
       </c>
-      <c r="M61">
+      <c r="M61" s="1">
         <v>30</v>
       </c>
-      <c r="N61">
+      <c r="N61" s="1">
         <v>60023</v>
       </c>
-      <c r="O61" s="1">
+      <c r="O61" s="2">
         <v>70300</v>
       </c>
-      <c r="P61">
+      <c r="P61" s="1">
         <v>202001</v>
       </c>
     </row>
     <row r="62" spans="1:16">
-      <c r="A62" s="1">
+      <c r="A62" s="2">
         <f t="shared" si="0"/>
         <v>100504</v>
       </c>
-      <c r="B62" s="1">
+      <c r="B62" s="2">
         <f t="shared" si="5"/>
         <v>1005</v>
       </c>
-      <c r="C62">
+      <c r="C62" s="1">
         <v>4</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D62" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E62" t="s">
-        <v>74</v>
-      </c>
-      <c r="F62" t="s">
+      <c r="E62" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F62" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G62" t="s">
+      <c r="G62" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H62">
+      <c r="H62" s="1">
         <v>4000</v>
       </c>
-      <c r="I62">
-        <v>3</v>
-      </c>
-      <c r="J62">
+      <c r="I62" s="1">
+        <v>3</v>
+      </c>
+      <c r="J62" s="1">
         <v>20</v>
       </c>
-      <c r="K62">
-        <v>3</v>
-      </c>
-      <c r="L62">
+      <c r="K62" s="1">
+        <v>3</v>
+      </c>
+      <c r="L62" s="1">
         <v>103</v>
       </c>
-      <c r="M62">
+      <c r="M62" s="1">
         <v>30</v>
       </c>
-      <c r="N62">
+      <c r="N62" s="1">
         <v>60024</v>
       </c>
-      <c r="O62" s="1">
+      <c r="O62" s="2">
         <v>70300</v>
       </c>
-      <c r="P62">
+      <c r="P62" s="1">
         <v>202001</v>
       </c>
     </row>
     <row r="63" spans="1:16">
-      <c r="A63" s="1">
+      <c r="A63" s="2">
         <f t="shared" si="0"/>
         <v>100505</v>
       </c>
-      <c r="B63" s="1">
+      <c r="B63" s="2">
         <f t="shared" si="5"/>
         <v>1005</v>
       </c>
-      <c r="C63">
+      <c r="C63" s="1">
         <v>5</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D63" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E63" t="s">
-        <v>74</v>
-      </c>
-      <c r="F63" t="s">
+      <c r="E63" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F63" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G63" t="s">
+      <c r="G63" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H63">
+      <c r="H63" s="1">
         <v>5000</v>
       </c>
-      <c r="I63">
-        <v>3</v>
-      </c>
-      <c r="J63">
+      <c r="I63" s="1">
+        <v>3</v>
+      </c>
+      <c r="J63" s="1">
         <v>20</v>
       </c>
-      <c r="K63">
-        <v>3</v>
-      </c>
-      <c r="L63">
+      <c r="K63" s="1">
+        <v>3</v>
+      </c>
+      <c r="L63" s="1">
         <v>103</v>
       </c>
-      <c r="M63">
+      <c r="M63" s="1">
         <v>30</v>
       </c>
-      <c r="N63">
+      <c r="N63" s="1">
         <v>60025</v>
       </c>
-      <c r="O63" s="1">
+      <c r="O63" s="2">
         <v>70300</v>
       </c>
-      <c r="P63">
+      <c r="P63" s="1">
         <v>202002</v>
       </c>
     </row>
     <row r="64" spans="1:16">
-      <c r="A64" s="1">
+      <c r="A64" s="2">
         <f t="shared" si="0"/>
         <v>100506</v>
       </c>
-      <c r="B64" s="1">
+      <c r="B64" s="2">
         <f t="shared" si="5"/>
         <v>1005</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="1">
         <v>6</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D64" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E64" t="s">
-        <v>74</v>
-      </c>
-      <c r="F64" t="s">
+      <c r="E64" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F64" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G64" t="s">
+      <c r="G64" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H64">
+      <c r="H64" s="1">
         <v>6000</v>
       </c>
-      <c r="I64">
-        <v>3</v>
-      </c>
-      <c r="J64">
+      <c r="I64" s="1">
+        <v>3</v>
+      </c>
+      <c r="J64" s="1">
         <v>20</v>
       </c>
-      <c r="K64">
-        <v>3</v>
-      </c>
-      <c r="L64">
+      <c r="K64" s="1">
+        <v>3</v>
+      </c>
+      <c r="L64" s="1">
         <v>103</v>
       </c>
-      <c r="M64">
+      <c r="M64" s="1">
         <v>30</v>
       </c>
-      <c r="N64">
+      <c r="N64" s="1">
         <v>60026</v>
       </c>
-      <c r="O64" s="1">
+      <c r="O64" s="2">
         <v>70300</v>
       </c>
-      <c r="P64">
+      <c r="P64" s="1">
         <v>202002</v>
       </c>
     </row>
     <row r="65" spans="1:17">
-      <c r="A65" s="1">
+      <c r="A65" s="2">
         <f t="shared" si="0"/>
         <v>100507</v>
       </c>
-      <c r="B65" s="1">
+      <c r="B65" s="2">
         <f t="shared" si="5"/>
         <v>1005</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="1">
         <v>7</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D65" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E65" t="s">
-        <v>74</v>
-      </c>
-      <c r="F65" t="s">
+      <c r="E65" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F65" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G65" t="s">
+      <c r="G65" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H65">
+      <c r="H65" s="1">
         <v>7000</v>
       </c>
-      <c r="I65">
-        <v>3</v>
-      </c>
-      <c r="J65">
+      <c r="I65" s="1">
+        <v>3</v>
+      </c>
+      <c r="J65" s="1">
         <v>20</v>
       </c>
-      <c r="K65">
-        <v>3</v>
-      </c>
-      <c r="L65">
+      <c r="K65" s="1">
+        <v>3</v>
+      </c>
+      <c r="L65" s="1">
         <v>103</v>
       </c>
-      <c r="M65">
+      <c r="M65" s="1">
         <v>30</v>
       </c>
-      <c r="N65">
+      <c r="N65" s="1">
         <v>60027</v>
       </c>
-      <c r="O65" s="1">
+      <c r="O65" s="2">
         <v>70300</v>
       </c>
-      <c r="P65">
+      <c r="P65" s="1">
         <v>202002</v>
       </c>
     </row>
     <row r="66" spans="1:17">
-      <c r="A66" s="1">
+      <c r="A66" s="2">
         <f t="shared" si="0"/>
         <v>100508</v>
       </c>
-      <c r="B66" s="1">
+      <c r="B66" s="2">
         <f t="shared" si="5"/>
         <v>1005</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="1">
         <v>8</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D66" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E66" t="s">
-        <v>74</v>
-      </c>
-      <c r="F66" t="s">
+      <c r="E66" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F66" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G66" t="s">
+      <c r="G66" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H66">
+      <c r="H66" s="1">
         <v>8000</v>
       </c>
-      <c r="I66">
-        <v>3</v>
-      </c>
-      <c r="J66">
+      <c r="I66" s="1">
+        <v>3</v>
+      </c>
+      <c r="J66" s="1">
         <v>20</v>
       </c>
-      <c r="K66">
-        <v>3</v>
-      </c>
-      <c r="L66">
+      <c r="K66" s="1">
+        <v>3</v>
+      </c>
+      <c r="L66" s="1">
         <v>103</v>
       </c>
-      <c r="M66">
+      <c r="M66" s="1">
         <v>30</v>
       </c>
-      <c r="N66">
+      <c r="N66" s="1">
         <v>60028</v>
       </c>
-      <c r="O66" s="1">
+      <c r="O66" s="2">
         <v>70300</v>
       </c>
-      <c r="P66">
+      <c r="P66" s="1">
         <v>202002</v>
       </c>
     </row>
     <row r="67" spans="1:17">
-      <c r="A67" s="1">
-        <f t="shared" ref="A67:A101" si="6">B67*100+C67</f>
+      <c r="A67" s="2">
+        <f t="shared" ref="A67:A104" si="6">B67*100+C67</f>
         <v>100509</v>
       </c>
-      <c r="B67" s="1">
+      <c r="B67" s="2">
         <f t="shared" si="5"/>
         <v>1005</v>
       </c>
-      <c r="C67">
+      <c r="C67" s="1">
         <v>9</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D67" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E67" t="s">
-        <v>74</v>
-      </c>
-      <c r="F67" t="s">
+      <c r="E67" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F67" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G67" t="s">
+      <c r="G67" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H67">
+      <c r="H67" s="1">
         <v>9000</v>
       </c>
-      <c r="I67">
-        <v>3</v>
-      </c>
-      <c r="J67">
+      <c r="I67" s="1">
+        <v>3</v>
+      </c>
+      <c r="J67" s="1">
         <v>20</v>
       </c>
-      <c r="K67">
-        <v>3</v>
-      </c>
-      <c r="L67">
+      <c r="K67" s="1">
+        <v>3</v>
+      </c>
+      <c r="L67" s="1">
         <v>103</v>
       </c>
-      <c r="M67">
+      <c r="M67" s="1">
         <v>30</v>
       </c>
-      <c r="N67">
+      <c r="N67" s="1">
         <v>60029</v>
       </c>
-      <c r="O67" s="1">
+      <c r="O67" s="2">
         <v>70300</v>
       </c>
-      <c r="P67">
+      <c r="P67" s="1">
         <v>202002</v>
       </c>
     </row>
     <row r="68" spans="1:17">
-      <c r="A68" s="1">
+      <c r="A68" s="2">
         <f t="shared" si="6"/>
         <v>100510</v>
       </c>
-      <c r="B68" s="1">
+      <c r="B68" s="2">
         <f t="shared" si="5"/>
         <v>1005</v>
       </c>
-      <c r="C68">
+      <c r="C68" s="1">
         <v>10</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D68" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E68" t="s">
-        <v>74</v>
-      </c>
-      <c r="F68" t="s">
+      <c r="E68" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F68" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G68" t="s">
+      <c r="G68" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H68">
+      <c r="H68" s="1">
         <v>10000</v>
       </c>
-      <c r="I68">
-        <v>3</v>
-      </c>
-      <c r="J68">
+      <c r="I68" s="1">
+        <v>3</v>
+      </c>
+      <c r="J68" s="1">
         <v>20</v>
       </c>
-      <c r="K68">
-        <v>3</v>
-      </c>
-      <c r="L68">
+      <c r="K68" s="1">
+        <v>3</v>
+      </c>
+      <c r="L68" s="1">
         <v>103</v>
       </c>
-      <c r="M68">
+      <c r="M68" s="1">
         <v>30</v>
       </c>
-      <c r="N68">
+      <c r="N68" s="1">
         <v>60030</v>
       </c>
-      <c r="O68" s="1">
+      <c r="O68" s="2">
         <v>70300</v>
       </c>
-      <c r="P68" t="s">
+      <c r="P68" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="Q68">
+      <c r="Q68" s="1">
         <v>16</v>
       </c>
     </row>
     <row r="69" spans="1:17">
-      <c r="A69" s="1">
+      <c r="A69" s="2">
         <f t="shared" si="6"/>
         <v>100600</v>
       </c>
-      <c r="B69" s="1">
+      <c r="B69" s="2">
         <f>B58+1</f>
         <v>1006</v>
       </c>
-      <c r="C69">
-        <v>0</v>
-      </c>
-      <c r="D69" t="s">
+      <c r="C69" s="1">
+        <v>0</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E69" t="s">
-        <v>74</v>
-      </c>
-      <c r="F69" t="s">
+      <c r="E69" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F69" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G69" t="s">
+      <c r="G69" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="H69">
-        <v>0</v>
-      </c>
-      <c r="I69">
-        <v>3</v>
-      </c>
-      <c r="J69">
-        <v>0</v>
-      </c>
-      <c r="K69">
-        <v>3</v>
-      </c>
-      <c r="L69">
+      <c r="H69" s="1">
+        <v>0</v>
+      </c>
+      <c r="I69" s="1">
+        <v>3</v>
+      </c>
+      <c r="J69" s="1">
+        <v>0</v>
+      </c>
+      <c r="K69" s="1">
+        <v>3</v>
+      </c>
+      <c r="L69" s="1">
         <v>104</v>
       </c>
-      <c r="M69">
-        <v>0</v>
-      </c>
-      <c r="N69" t="s">
-        <v>74</v>
-      </c>
-      <c r="O69" t="s">
-        <v>74</v>
-      </c>
-      <c r="P69" t="s">
+      <c r="M69" s="1">
+        <v>0</v>
+      </c>
+      <c r="N69" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O69" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P69" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="70" spans="1:17">
-      <c r="A70" s="1">
+      <c r="A70" s="2">
         <f t="shared" si="6"/>
         <v>100601</v>
       </c>
-      <c r="B70" s="1">
+      <c r="B70" s="2">
         <f t="shared" ref="B70:B79" si="7">B69</f>
         <v>1006</v>
       </c>
-      <c r="C70">
+      <c r="C70" s="1">
         <v>1</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D70" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E70" t="s">
-        <v>74</v>
-      </c>
-      <c r="F70" t="s">
+      <c r="E70" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F70" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G70" t="s">
+      <c r="G70" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="H70">
-        <v>0</v>
-      </c>
-      <c r="I70">
-        <v>3</v>
-      </c>
-      <c r="J70">
-        <v>0</v>
-      </c>
-      <c r="K70">
-        <v>3</v>
-      </c>
-      <c r="L70">
+      <c r="H70" s="1">
+        <v>0</v>
+      </c>
+      <c r="I70" s="1">
+        <v>3</v>
+      </c>
+      <c r="J70" s="1">
+        <v>0</v>
+      </c>
+      <c r="K70" s="1">
+        <v>3</v>
+      </c>
+      <c r="L70" s="1">
         <v>104</v>
       </c>
-      <c r="M70">
-        <v>0</v>
-      </c>
-      <c r="N70" t="s">
+      <c r="M70" s="1">
+        <v>0</v>
+      </c>
+      <c r="N70" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="O70" t="s">
-        <v>74</v>
-      </c>
-      <c r="P70" t="s">
+      <c r="O70" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P70" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="71" spans="1:17">
-      <c r="A71" s="1">
+      <c r="A71" s="2">
         <f t="shared" si="6"/>
         <v>100602</v>
       </c>
-      <c r="B71" s="1">
+      <c r="B71" s="2">
         <f t="shared" si="7"/>
         <v>1006</v>
       </c>
-      <c r="C71">
+      <c r="C71" s="1">
         <v>2</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D71" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E71" t="s">
-        <v>74</v>
-      </c>
-      <c r="F71" t="s">
+      <c r="E71" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F71" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G71" t="s">
+      <c r="G71" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="H71">
-        <v>0</v>
-      </c>
-      <c r="I71">
-        <v>3</v>
-      </c>
-      <c r="J71">
-        <v>0</v>
-      </c>
-      <c r="K71">
-        <v>3</v>
-      </c>
-      <c r="L71">
+      <c r="H71" s="1">
+        <v>0</v>
+      </c>
+      <c r="I71" s="1">
+        <v>3</v>
+      </c>
+      <c r="J71" s="1">
+        <v>0</v>
+      </c>
+      <c r="K71" s="1">
+        <v>3</v>
+      </c>
+      <c r="L71" s="1">
         <v>104</v>
       </c>
-      <c r="M71">
-        <v>0</v>
-      </c>
-      <c r="N71" t="s">
+      <c r="M71" s="1">
+        <v>0</v>
+      </c>
+      <c r="N71" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="O71" t="s">
-        <v>74</v>
-      </c>
-      <c r="P71" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17">
-      <c r="A72" s="1">
+      <c r="O71" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P71" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="72" ht="27" spans="1:17">
+      <c r="A72" s="2">
         <f t="shared" si="6"/>
         <v>100603</v>
       </c>
-      <c r="B72" s="1">
+      <c r="B72" s="2">
         <f t="shared" si="7"/>
         <v>1006</v>
       </c>
-      <c r="C72">
-        <v>3</v>
-      </c>
-      <c r="D72" t="s">
+      <c r="C72" s="1">
+        <v>3</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E72" t="s">
-        <v>74</v>
-      </c>
-      <c r="F72" t="s">
+      <c r="E72" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F72" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G72" t="s">
+      <c r="G72" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="H72">
-        <v>0</v>
-      </c>
-      <c r="I72">
-        <v>3</v>
-      </c>
-      <c r="J72">
-        <v>0</v>
-      </c>
-      <c r="K72">
-        <v>3</v>
-      </c>
-      <c r="L72">
+      <c r="H72" s="1">
+        <v>0</v>
+      </c>
+      <c r="I72" s="1">
+        <v>3</v>
+      </c>
+      <c r="J72" s="1">
+        <v>0</v>
+      </c>
+      <c r="K72" s="1">
+        <v>3</v>
+      </c>
+      <c r="L72" s="1">
         <v>104</v>
       </c>
-      <c r="M72">
-        <v>0</v>
-      </c>
-      <c r="N72" t="s">
+      <c r="M72" s="1">
+        <v>0</v>
+      </c>
+      <c r="N72" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="O72" t="s">
-        <v>74</v>
-      </c>
-      <c r="P72" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="73" spans="1:17">
-      <c r="A73" s="1">
+      <c r="O72" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P72" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="73" ht="27" spans="1:17">
+      <c r="A73" s="2">
         <f t="shared" si="6"/>
         <v>100604</v>
       </c>
-      <c r="B73" s="1">
+      <c r="B73" s="2">
         <f t="shared" si="7"/>
         <v>1006</v>
       </c>
-      <c r="C73">
+      <c r="C73" s="1">
         <v>4</v>
       </c>
-      <c r="D73" t="s">
+      <c r="D73" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E73" t="s">
-        <v>74</v>
-      </c>
-      <c r="F73" t="s">
+      <c r="E73" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F73" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G73" t="s">
+      <c r="G73" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="H73">
-        <v>0</v>
-      </c>
-      <c r="I73">
-        <v>3</v>
-      </c>
-      <c r="J73">
-        <v>0</v>
-      </c>
-      <c r="K73">
-        <v>3</v>
-      </c>
-      <c r="L73">
+      <c r="H73" s="1">
+        <v>0</v>
+      </c>
+      <c r="I73" s="1">
+        <v>3</v>
+      </c>
+      <c r="J73" s="1">
+        <v>0</v>
+      </c>
+      <c r="K73" s="1">
+        <v>3</v>
+      </c>
+      <c r="L73" s="1">
         <v>104</v>
       </c>
-      <c r="M73">
-        <v>0</v>
-      </c>
-      <c r="N73" t="s">
+      <c r="M73" s="1">
+        <v>0</v>
+      </c>
+      <c r="N73" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="O73" t="s">
-        <v>74</v>
-      </c>
-      <c r="P73" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="74" spans="1:17">
-      <c r="A74" s="1">
+      <c r="O73" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P73" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="74" ht="27" spans="1:17">
+      <c r="A74" s="2">
         <f t="shared" si="6"/>
         <v>100605</v>
       </c>
-      <c r="B74" s="1">
+      <c r="B74" s="2">
         <f t="shared" si="7"/>
         <v>1006</v>
       </c>
-      <c r="C74">
+      <c r="C74" s="1">
         <v>5</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D74" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E74" t="s">
-        <v>74</v>
-      </c>
-      <c r="F74" t="s">
+      <c r="E74" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F74" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G74" t="s">
+      <c r="G74" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="H74">
-        <v>0</v>
-      </c>
-      <c r="I74">
-        <v>3</v>
-      </c>
-      <c r="J74">
-        <v>0</v>
-      </c>
-      <c r="K74">
-        <v>3</v>
-      </c>
-      <c r="L74">
+      <c r="H74" s="1">
+        <v>0</v>
+      </c>
+      <c r="I74" s="1">
+        <v>3</v>
+      </c>
+      <c r="J74" s="1">
+        <v>0</v>
+      </c>
+      <c r="K74" s="1">
+        <v>3</v>
+      </c>
+      <c r="L74" s="1">
         <v>104</v>
       </c>
-      <c r="M74">
-        <v>0</v>
-      </c>
-      <c r="N74" t="s">
+      <c r="M74" s="1">
+        <v>0</v>
+      </c>
+      <c r="N74" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="O74" t="s">
-        <v>74</v>
-      </c>
-      <c r="P74" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="75" spans="1:17">
-      <c r="A75" s="1">
+      <c r="O74" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P74" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="75" ht="27" spans="1:17">
+      <c r="A75" s="2">
         <f t="shared" si="6"/>
         <v>100606</v>
       </c>
-      <c r="B75" s="1">
+      <c r="B75" s="2">
         <f t="shared" si="7"/>
         <v>1006</v>
       </c>
-      <c r="C75">
+      <c r="C75" s="1">
         <v>6</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D75" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E75" t="s">
-        <v>74</v>
-      </c>
-      <c r="F75" t="s">
+      <c r="E75" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F75" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G75" t="s">
+      <c r="G75" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="H75">
-        <v>0</v>
-      </c>
-      <c r="I75">
-        <v>3</v>
-      </c>
-      <c r="J75">
-        <v>0</v>
-      </c>
-      <c r="K75">
-        <v>3</v>
-      </c>
-      <c r="L75">
+      <c r="H75" s="1">
+        <v>0</v>
+      </c>
+      <c r="I75" s="1">
+        <v>3</v>
+      </c>
+      <c r="J75" s="1">
+        <v>0</v>
+      </c>
+      <c r="K75" s="1">
+        <v>3</v>
+      </c>
+      <c r="L75" s="1">
         <v>104</v>
       </c>
-      <c r="M75">
-        <v>0</v>
-      </c>
-      <c r="N75" t="s">
+      <c r="M75" s="1">
+        <v>0</v>
+      </c>
+      <c r="N75" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="O75" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="76" spans="1:17">
-      <c r="A76" s="1">
+      <c r="O75" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" ht="27" spans="1:17">
+      <c r="A76" s="2">
         <f t="shared" si="6"/>
         <v>100607</v>
       </c>
-      <c r="B76" s="1">
+      <c r="B76" s="2">
         <f t="shared" si="7"/>
         <v>1006</v>
       </c>
-      <c r="C76">
+      <c r="C76" s="1">
         <v>7</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D76" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E76" t="s">
-        <v>74</v>
-      </c>
-      <c r="F76" t="s">
+      <c r="E76" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F76" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G76" t="s">
+      <c r="G76" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="H76">
-        <v>0</v>
-      </c>
-      <c r="I76">
-        <v>3</v>
-      </c>
-      <c r="J76">
-        <v>0</v>
-      </c>
-      <c r="K76">
-        <v>3</v>
-      </c>
-      <c r="L76">
+      <c r="H76" s="1">
+        <v>0</v>
+      </c>
+      <c r="I76" s="1">
+        <v>3</v>
+      </c>
+      <c r="J76" s="1">
+        <v>0</v>
+      </c>
+      <c r="K76" s="1">
+        <v>3</v>
+      </c>
+      <c r="L76" s="1">
         <v>104</v>
       </c>
-      <c r="M76">
-        <v>0</v>
-      </c>
-      <c r="N76" t="s">
+      <c r="M76" s="1">
+        <v>0</v>
+      </c>
+      <c r="N76" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="O76" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="77" spans="1:17">
-      <c r="A77" s="1">
+      <c r="O76" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="77" ht="27" spans="1:17">
+      <c r="A77" s="2">
         <f t="shared" si="6"/>
         <v>100608</v>
       </c>
-      <c r="B77" s="1">
+      <c r="B77" s="2">
         <f t="shared" si="7"/>
         <v>1006</v>
       </c>
-      <c r="C77">
+      <c r="C77" s="1">
         <v>8</v>
       </c>
-      <c r="D77" t="s">
+      <c r="D77" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E77" t="s">
-        <v>74</v>
-      </c>
-      <c r="F77" t="s">
+      <c r="E77" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F77" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G77" t="s">
+      <c r="G77" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="H77">
-        <v>0</v>
-      </c>
-      <c r="I77">
-        <v>3</v>
-      </c>
-      <c r="J77">
-        <v>0</v>
-      </c>
-      <c r="K77">
-        <v>3</v>
-      </c>
-      <c r="L77">
+      <c r="H77" s="1">
+        <v>0</v>
+      </c>
+      <c r="I77" s="1">
+        <v>3</v>
+      </c>
+      <c r="J77" s="1">
+        <v>0</v>
+      </c>
+      <c r="K77" s="1">
+        <v>3</v>
+      </c>
+      <c r="L77" s="1">
         <v>104</v>
       </c>
-      <c r="M77">
-        <v>0</v>
-      </c>
-      <c r="N77" t="s">
+      <c r="M77" s="1">
+        <v>0</v>
+      </c>
+      <c r="N77" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="O77" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="78" spans="1:17">
-      <c r="A78" s="1">
+      <c r="O77" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="78" ht="27" spans="1:17">
+      <c r="A78" s="2">
         <f t="shared" si="6"/>
         <v>100609</v>
       </c>
-      <c r="B78" s="1">
+      <c r="B78" s="2">
         <f t="shared" si="7"/>
         <v>1006</v>
       </c>
-      <c r="C78">
+      <c r="C78" s="1">
         <v>9</v>
       </c>
-      <c r="D78" t="s">
+      <c r="D78" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E78" t="s">
-        <v>74</v>
-      </c>
-      <c r="F78" t="s">
+      <c r="E78" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F78" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G78" t="s">
+      <c r="G78" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="H78">
-        <v>0</v>
-      </c>
-      <c r="I78">
-        <v>3</v>
-      </c>
-      <c r="J78">
-        <v>0</v>
-      </c>
-      <c r="K78">
-        <v>3</v>
-      </c>
-      <c r="L78">
+      <c r="H78" s="1">
+        <v>0</v>
+      </c>
+      <c r="I78" s="1">
+        <v>3</v>
+      </c>
+      <c r="J78" s="1">
+        <v>0</v>
+      </c>
+      <c r="K78" s="1">
+        <v>3</v>
+      </c>
+      <c r="L78" s="1">
         <v>104</v>
       </c>
-      <c r="M78">
-        <v>0</v>
-      </c>
-      <c r="N78" t="s">
+      <c r="M78" s="1">
+        <v>0</v>
+      </c>
+      <c r="N78" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="O78" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="79" spans="1:17">
-      <c r="A79" s="1">
+      <c r="O78" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="79" ht="27" spans="1:17">
+      <c r="A79" s="2">
         <f t="shared" si="6"/>
         <v>100610</v>
       </c>
-      <c r="B79" s="1">
+      <c r="B79" s="2">
         <f t="shared" si="7"/>
         <v>1006</v>
       </c>
-      <c r="C79">
+      <c r="C79" s="1">
         <v>10</v>
       </c>
-      <c r="D79" t="s">
+      <c r="D79" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E79" t="s">
-        <v>74</v>
-      </c>
-      <c r="F79" t="s">
+      <c r="E79" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F79" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G79" t="s">
+      <c r="G79" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="H79">
-        <v>0</v>
-      </c>
-      <c r="I79">
-        <v>3</v>
-      </c>
-      <c r="J79">
-        <v>0</v>
-      </c>
-      <c r="K79">
-        <v>3</v>
-      </c>
-      <c r="L79">
+      <c r="H79" s="1">
+        <v>0</v>
+      </c>
+      <c r="I79" s="1">
+        <v>3</v>
+      </c>
+      <c r="J79" s="1">
+        <v>0</v>
+      </c>
+      <c r="K79" s="1">
+        <v>3</v>
+      </c>
+      <c r="L79" s="1">
         <v>104</v>
       </c>
-      <c r="M79">
-        <v>0</v>
-      </c>
-      <c r="N79" t="s">
+      <c r="M79" s="1">
+        <v>0</v>
+      </c>
+      <c r="N79" s="1" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="80" spans="1:17">
-      <c r="A80" s="1">
+      <c r="A80" s="2">
         <f t="shared" si="6"/>
         <v>100700</v>
       </c>
-      <c r="B80" s="1">
+      <c r="B80" s="2">
         <f>B69+1</f>
         <v>1007</v>
       </c>
-      <c r="C80">
-        <v>0</v>
-      </c>
-      <c r="D80" t="s">
+      <c r="C80" s="1">
+        <v>0</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E80" t="s">
-        <v>74</v>
-      </c>
-      <c r="F80" t="s">
+      <c r="E80" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F80" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G80" t="s">
+      <c r="G80" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="H80">
-        <v>0</v>
-      </c>
-      <c r="I80">
+      <c r="H80" s="1">
+        <v>0</v>
+      </c>
+      <c r="I80" s="1">
         <v>4</v>
       </c>
-      <c r="J80">
-        <v>0</v>
-      </c>
-      <c r="K80">
-        <v>3</v>
-      </c>
-      <c r="L80">
-        <v>0</v>
-      </c>
-      <c r="M80">
-        <v>0</v>
-      </c>
-      <c r="N80" t="s">
-        <v>74</v>
-      </c>
-      <c r="O80" t="s">
-        <v>74</v>
-      </c>
-      <c r="P80" t="s">
+      <c r="J80" s="1">
+        <v>0</v>
+      </c>
+      <c r="K80" s="1">
+        <v>3</v>
+      </c>
+      <c r="L80" s="1">
+        <v>0</v>
+      </c>
+      <c r="M80" s="1">
+        <v>0</v>
+      </c>
+      <c r="N80" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O80" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P80" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="81" spans="1:16">
-      <c r="A81" s="1">
+      <c r="A81" s="2">
         <f t="shared" si="6"/>
         <v>100701</v>
       </c>
-      <c r="B81" s="1">
+      <c r="B81" s="2">
         <f t="shared" ref="B81:B90" si="8">B80</f>
         <v>1007</v>
       </c>
-      <c r="C81">
+      <c r="C81" s="1">
         <v>1</v>
       </c>
-      <c r="D81" t="s">
+      <c r="D81" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E81" t="s">
-        <v>74</v>
-      </c>
-      <c r="F81" t="s">
+      <c r="E81" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F81" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G81" t="s">
+      <c r="G81" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="H81">
+      <c r="H81" s="1">
         <v>3000</v>
       </c>
-      <c r="I81">
+      <c r="I81" s="1">
         <v>4</v>
       </c>
-      <c r="J81">
-        <v>0</v>
-      </c>
-      <c r="K81">
-        <v>3</v>
-      </c>
-      <c r="L81">
-        <v>0</v>
-      </c>
-      <c r="M81">
-        <v>0</v>
-      </c>
-      <c r="N81">
+      <c r="J81" s="1">
+        <v>0</v>
+      </c>
+      <c r="K81" s="1">
+        <v>3</v>
+      </c>
+      <c r="L81" s="1">
+        <v>0</v>
+      </c>
+      <c r="M81" s="1">
+        <v>0</v>
+      </c>
+      <c r="N81" s="1">
         <v>60031</v>
       </c>
-      <c r="O81">
+      <c r="O81" s="1">
         <v>40005</v>
       </c>
-      <c r="P81" t="s">
+      <c r="P81" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="82" spans="1:16">
-      <c r="A82" s="1">
+      <c r="A82" s="2">
         <f t="shared" si="6"/>
         <v>100702</v>
       </c>
-      <c r="B82" s="1">
+      <c r="B82" s="2">
         <f t="shared" si="8"/>
         <v>1007</v>
       </c>
-      <c r="C82">
+      <c r="C82" s="1">
         <v>2</v>
       </c>
-      <c r="D82" t="s">
+      <c r="D82" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E82" t="s">
-        <v>74</v>
-      </c>
-      <c r="F82" t="s">
+      <c r="E82" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F82" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G82" t="s">
+      <c r="G82" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="H82">
+      <c r="H82" s="1">
         <v>3500</v>
       </c>
-      <c r="I82">
+      <c r="I82" s="1">
         <v>4</v>
       </c>
-      <c r="J82">
-        <v>0</v>
-      </c>
-      <c r="K82">
-        <v>3</v>
-      </c>
-      <c r="L82">
-        <v>0</v>
-      </c>
-      <c r="M82">
-        <v>0</v>
-      </c>
-      <c r="N82">
+      <c r="J82" s="1">
+        <v>0</v>
+      </c>
+      <c r="K82" s="1">
+        <v>3</v>
+      </c>
+      <c r="L82" s="1">
+        <v>0</v>
+      </c>
+      <c r="M82" s="1">
+        <v>0</v>
+      </c>
+      <c r="N82" s="1">
         <v>60032</v>
       </c>
-      <c r="O82">
+      <c r="O82" s="1">
         <v>40005</v>
       </c>
-      <c r="P82" t="s">
+      <c r="P82" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="83" spans="1:16">
-      <c r="A83" s="1">
+      <c r="A83" s="2">
         <f t="shared" si="6"/>
         <v>100703</v>
       </c>
-      <c r="B83" s="1">
+      <c r="B83" s="2">
         <f t="shared" si="8"/>
         <v>1007</v>
       </c>
-      <c r="C83">
-        <v>3</v>
-      </c>
-      <c r="D83" t="s">
+      <c r="C83" s="1">
+        <v>3</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E83" t="s">
-        <v>74</v>
-      </c>
-      <c r="F83" t="s">
+      <c r="E83" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F83" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G83" t="s">
+      <c r="G83" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="H83">
+      <c r="H83" s="1">
         <v>4000</v>
       </c>
-      <c r="I83">
+      <c r="I83" s="1">
         <v>4</v>
       </c>
-      <c r="J83">
-        <v>0</v>
-      </c>
-      <c r="K83">
-        <v>3</v>
-      </c>
-      <c r="L83">
-        <v>0</v>
-      </c>
-      <c r="M83">
-        <v>0</v>
-      </c>
-      <c r="N83">
+      <c r="J83" s="1">
+        <v>0</v>
+      </c>
+      <c r="K83" s="1">
+        <v>3</v>
+      </c>
+      <c r="L83" s="1">
+        <v>0</v>
+      </c>
+      <c r="M83" s="1">
+        <v>0</v>
+      </c>
+      <c r="N83" s="1">
         <v>60033</v>
       </c>
-      <c r="O83" t="s">
+      <c r="O83" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="P83" t="s">
+      <c r="P83" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="84" spans="1:16">
-      <c r="A84" s="1">
+      <c r="A84" s="2">
         <f t="shared" si="6"/>
         <v>100704</v>
       </c>
-      <c r="B84" s="1">
+      <c r="B84" s="2">
         <f t="shared" si="8"/>
         <v>1007</v>
       </c>
-      <c r="C84">
+      <c r="C84" s="1">
         <v>4</v>
       </c>
-      <c r="D84" t="s">
+      <c r="D84" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E84" t="s">
-        <v>74</v>
-      </c>
-      <c r="F84" t="s">
+      <c r="E84" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F84" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G84" t="s">
+      <c r="G84" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="H84">
+      <c r="H84" s="1">
         <v>4500</v>
       </c>
-      <c r="I84">
+      <c r="I84" s="1">
         <v>4</v>
       </c>
-      <c r="J84">
-        <v>0</v>
-      </c>
-      <c r="K84">
-        <v>3</v>
-      </c>
-      <c r="L84">
-        <v>0</v>
-      </c>
-      <c r="M84">
-        <v>0</v>
-      </c>
-      <c r="N84">
+      <c r="J84" s="1">
+        <v>0</v>
+      </c>
+      <c r="K84" s="1">
+        <v>3</v>
+      </c>
+      <c r="L84" s="1">
+        <v>0</v>
+      </c>
+      <c r="M84" s="1">
+        <v>0</v>
+      </c>
+      <c r="N84" s="1">
         <v>60034</v>
       </c>
-      <c r="O84" t="s">
+      <c r="O84" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="P84" t="s">
+      <c r="P84" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="85" spans="1:16">
-      <c r="A85" s="1">
+      <c r="A85" s="2">
         <f t="shared" si="6"/>
         <v>100705</v>
       </c>
-      <c r="B85" s="1">
+      <c r="B85" s="2">
         <f t="shared" si="8"/>
         <v>1007</v>
       </c>
-      <c r="C85">
+      <c r="C85" s="1">
         <v>5</v>
       </c>
-      <c r="D85" t="s">
+      <c r="D85" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E85" t="s">
-        <v>74</v>
-      </c>
-      <c r="F85" t="s">
+      <c r="E85" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F85" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G85" t="s">
+      <c r="G85" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="H85">
+      <c r="H85" s="1">
         <v>5000</v>
       </c>
-      <c r="I85">
+      <c r="I85" s="1">
         <v>4</v>
       </c>
-      <c r="J85">
-        <v>0</v>
-      </c>
-      <c r="K85">
-        <v>3</v>
-      </c>
-      <c r="L85">
-        <v>0</v>
-      </c>
-      <c r="M85">
-        <v>0</v>
-      </c>
-      <c r="N85">
+      <c r="J85" s="1">
+        <v>0</v>
+      </c>
+      <c r="K85" s="1">
+        <v>3</v>
+      </c>
+      <c r="L85" s="1">
+        <v>0</v>
+      </c>
+      <c r="M85" s="1">
+        <v>0</v>
+      </c>
+      <c r="N85" s="1">
         <v>60035</v>
       </c>
-      <c r="O85" t="s">
+      <c r="O85" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="P85" t="s">
+      <c r="P85" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="86" spans="1:16">
-      <c r="A86" s="1">
+      <c r="A86" s="2">
         <f t="shared" si="6"/>
         <v>100706</v>
       </c>
-      <c r="B86" s="1">
+      <c r="B86" s="2">
         <f t="shared" si="8"/>
         <v>1007</v>
       </c>
-      <c r="C86">
+      <c r="C86" s="1">
         <v>6</v>
       </c>
-      <c r="D86" t="s">
+      <c r="D86" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E86" t="s">
-        <v>74</v>
-      </c>
-      <c r="F86" t="s">
+      <c r="E86" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F86" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G86" t="s">
+      <c r="G86" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="H86">
+      <c r="H86" s="1">
         <v>5500</v>
       </c>
-      <c r="I86">
+      <c r="I86" s="1">
         <v>4</v>
       </c>
-      <c r="J86">
-        <v>0</v>
-      </c>
-      <c r="K86">
-        <v>3</v>
-      </c>
-      <c r="L86">
-        <v>0</v>
-      </c>
-      <c r="M86">
-        <v>0</v>
-      </c>
-      <c r="N86">
+      <c r="J86" s="1">
+        <v>0</v>
+      </c>
+      <c r="K86" s="1">
+        <v>3</v>
+      </c>
+      <c r="L86" s="1">
+        <v>0</v>
+      </c>
+      <c r="M86" s="1">
+        <v>0</v>
+      </c>
+      <c r="N86" s="1">
         <v>60036</v>
       </c>
-      <c r="O86" t="s">
+      <c r="O86" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="P86" t="s">
+      <c r="P86" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="87" spans="1:16">
-      <c r="A87" s="1">
+      <c r="A87" s="2">
         <f t="shared" si="6"/>
         <v>100707</v>
       </c>
-      <c r="B87" s="1">
+      <c r="B87" s="2">
         <f t="shared" si="8"/>
         <v>1007</v>
       </c>
-      <c r="C87">
+      <c r="C87" s="1">
         <v>7</v>
       </c>
-      <c r="D87" t="s">
+      <c r="D87" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E87" t="s">
-        <v>74</v>
-      </c>
-      <c r="F87" t="s">
+      <c r="E87" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F87" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G87" t="s">
+      <c r="G87" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="H87">
+      <c r="H87" s="1">
         <v>6000</v>
       </c>
-      <c r="I87">
+      <c r="I87" s="1">
         <v>4</v>
       </c>
-      <c r="J87">
-        <v>0</v>
-      </c>
-      <c r="K87">
-        <v>3</v>
-      </c>
-      <c r="L87">
-        <v>0</v>
-      </c>
-      <c r="M87">
-        <v>0</v>
-      </c>
-      <c r="N87">
+      <c r="J87" s="1">
+        <v>0</v>
+      </c>
+      <c r="K87" s="1">
+        <v>3</v>
+      </c>
+      <c r="L87" s="1">
+        <v>0</v>
+      </c>
+      <c r="M87" s="1">
+        <v>0</v>
+      </c>
+      <c r="N87" s="1">
         <v>60037</v>
       </c>
-      <c r="O87" t="s">
+      <c r="O87" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="P87" t="s">
+      <c r="P87" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="88" spans="1:16">
-      <c r="A88" s="1">
+      <c r="A88" s="2">
         <f t="shared" si="6"/>
         <v>100708</v>
       </c>
-      <c r="B88" s="1">
+      <c r="B88" s="2">
         <f t="shared" si="8"/>
         <v>1007</v>
       </c>
-      <c r="C88">
+      <c r="C88" s="1">
         <v>8</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D88" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E88" t="s">
-        <v>74</v>
-      </c>
-      <c r="F88" t="s">
+      <c r="E88" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F88" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G88" t="s">
+      <c r="G88" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="H88">
+      <c r="H88" s="1">
         <v>6500</v>
       </c>
-      <c r="I88">
+      <c r="I88" s="1">
         <v>4</v>
       </c>
-      <c r="J88">
-        <v>0</v>
-      </c>
-      <c r="K88">
-        <v>3</v>
-      </c>
-      <c r="L88">
-        <v>0</v>
-      </c>
-      <c r="M88">
-        <v>0</v>
-      </c>
-      <c r="N88">
+      <c r="J88" s="1">
+        <v>0</v>
+      </c>
+      <c r="K88" s="1">
+        <v>3</v>
+      </c>
+      <c r="L88" s="1">
+        <v>0</v>
+      </c>
+      <c r="M88" s="1">
+        <v>0</v>
+      </c>
+      <c r="N88" s="1">
         <v>60038</v>
       </c>
-      <c r="O88" t="s">
+      <c r="O88" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="P88" t="s">
+      <c r="P88" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="89" spans="1:16">
-      <c r="A89" s="1">
+      <c r="A89" s="2">
         <f t="shared" si="6"/>
         <v>100709</v>
       </c>
-      <c r="B89" s="1">
+      <c r="B89" s="2">
         <f t="shared" si="8"/>
         <v>1007</v>
       </c>
-      <c r="C89">
+      <c r="C89" s="1">
         <v>9</v>
       </c>
-      <c r="D89" t="s">
+      <c r="D89" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E89" t="s">
-        <v>74</v>
-      </c>
-      <c r="F89" t="s">
+      <c r="E89" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F89" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G89" t="s">
+      <c r="G89" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="H89">
+      <c r="H89" s="1">
         <v>7000</v>
       </c>
-      <c r="I89">
+      <c r="I89" s="1">
         <v>4</v>
       </c>
-      <c r="J89">
-        <v>0</v>
-      </c>
-      <c r="K89">
-        <v>3</v>
-      </c>
-      <c r="L89">
-        <v>0</v>
-      </c>
-      <c r="M89">
-        <v>0</v>
-      </c>
-      <c r="N89">
+      <c r="J89" s="1">
+        <v>0</v>
+      </c>
+      <c r="K89" s="1">
+        <v>3</v>
+      </c>
+      <c r="L89" s="1">
+        <v>0</v>
+      </c>
+      <c r="M89" s="1">
+        <v>0</v>
+      </c>
+      <c r="N89" s="1">
         <v>60039</v>
       </c>
-      <c r="O89" t="s">
+      <c r="O89" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="P89" t="s">
+      <c r="P89" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="90" spans="1:16">
-      <c r="A90" s="1">
+      <c r="A90" s="2">
         <f t="shared" si="6"/>
         <v>100710</v>
       </c>
-      <c r="B90" s="1">
+      <c r="B90" s="2">
         <f t="shared" si="8"/>
         <v>1007</v>
       </c>
-      <c r="C90">
+      <c r="C90" s="1">
         <v>10</v>
       </c>
-      <c r="D90" t="s">
+      <c r="D90" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E90" t="s">
-        <v>74</v>
-      </c>
-      <c r="F90" t="s">
+      <c r="E90" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F90" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G90" t="s">
+      <c r="G90" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="H90">
+      <c r="H90" s="1">
         <v>7500</v>
       </c>
-      <c r="I90">
+      <c r="I90" s="1">
         <v>4</v>
       </c>
-      <c r="J90">
-        <v>0</v>
-      </c>
-      <c r="K90">
-        <v>3</v>
-      </c>
-      <c r="L90">
-        <v>0</v>
-      </c>
-      <c r="M90">
-        <v>0</v>
-      </c>
-      <c r="N90" t="s">
+      <c r="J90" s="1">
+        <v>0</v>
+      </c>
+      <c r="K90" s="1">
+        <v>3</v>
+      </c>
+      <c r="L90" s="1">
+        <v>0</v>
+      </c>
+      <c r="M90" s="1">
+        <v>0</v>
+      </c>
+      <c r="N90" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="O90" t="s">
+      <c r="O90" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="P90" t="s">
+      <c r="P90" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="91" spans="1:16">
-      <c r="A91" s="1">
+      <c r="A91" s="2">
         <f t="shared" si="6"/>
         <v>100800</v>
       </c>
-      <c r="B91" s="1">
+      <c r="B91" s="2">
         <f>B80+1</f>
         <v>1008</v>
       </c>
-      <c r="C91">
-        <v>0</v>
-      </c>
-      <c r="D91" t="s">
+      <c r="C91" s="1">
+        <v>0</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E91" t="s">
-        <v>74</v>
-      </c>
-      <c r="F91" t="s">
+      <c r="E91" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F91" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G91" t="s">
+      <c r="G91" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="H91">
-        <v>0</v>
-      </c>
-      <c r="I91">
+      <c r="H91" s="1">
+        <v>0</v>
+      </c>
+      <c r="I91" s="1">
         <v>4</v>
       </c>
-      <c r="J91">
-        <v>0</v>
-      </c>
-      <c r="K91">
-        <v>3</v>
-      </c>
-      <c r="L91">
-        <v>0</v>
-      </c>
-      <c r="M91">
-        <v>0</v>
-      </c>
-      <c r="N91" t="s">
-        <v>74</v>
-      </c>
-      <c r="O91" t="s">
-        <v>74</v>
-      </c>
-      <c r="P91" t="s">
+      <c r="J91" s="1">
+        <v>0</v>
+      </c>
+      <c r="K91" s="1">
+        <v>3</v>
+      </c>
+      <c r="L91" s="1">
+        <v>0</v>
+      </c>
+      <c r="M91" s="1">
+        <v>0</v>
+      </c>
+      <c r="N91" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O91" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P91" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="92" spans="1:16">
-      <c r="A92" s="1">
+      <c r="A92" s="2">
         <f t="shared" si="6"/>
         <v>100801</v>
       </c>
-      <c r="B92" s="1">
+      <c r="B92" s="2">
         <f t="shared" ref="B92:B101" si="9">B91</f>
         <v>1008</v>
       </c>
-      <c r="C92">
+      <c r="C92" s="1">
         <v>1</v>
       </c>
-      <c r="D92" t="s">
+      <c r="D92" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E92" t="s">
-        <v>74</v>
-      </c>
-      <c r="F92" t="s">
+      <c r="E92" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F92" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G92" t="s">
+      <c r="G92" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="H92">
-        <v>0</v>
-      </c>
-      <c r="I92">
+      <c r="H92" s="1">
+        <v>0</v>
+      </c>
+      <c r="I92" s="1">
         <v>4</v>
       </c>
-      <c r="J92">
-        <v>0</v>
-      </c>
-      <c r="K92">
-        <v>3</v>
-      </c>
-      <c r="L92">
-        <v>0</v>
-      </c>
-      <c r="M92">
-        <v>0</v>
-      </c>
-      <c r="N92" t="s">
+      <c r="J92" s="1">
+        <v>0</v>
+      </c>
+      <c r="K92" s="1">
+        <v>3</v>
+      </c>
+      <c r="L92" s="1">
+        <v>0</v>
+      </c>
+      <c r="M92" s="1">
+        <v>0</v>
+      </c>
+      <c r="N92" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="P92" t="s">
+      <c r="P92" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="93" spans="1:16">
-      <c r="A93" s="1">
+      <c r="A93" s="2">
         <f t="shared" si="6"/>
         <v>100802</v>
       </c>
-      <c r="B93" s="1">
+      <c r="B93" s="2">
         <f t="shared" si="9"/>
         <v>1008</v>
       </c>
-      <c r="C93">
+      <c r="C93" s="1">
         <v>2</v>
       </c>
-      <c r="D93" t="s">
+      <c r="D93" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E93" t="s">
-        <v>74</v>
-      </c>
-      <c r="F93" t="s">
+      <c r="E93" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F93" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G93" t="s">
+      <c r="G93" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="H93">
-        <v>0</v>
-      </c>
-      <c r="I93">
+      <c r="H93" s="1">
+        <v>0</v>
+      </c>
+      <c r="I93" s="1">
         <v>4</v>
       </c>
-      <c r="J93">
-        <v>0</v>
-      </c>
-      <c r="K93">
-        <v>3</v>
-      </c>
-      <c r="L93">
-        <v>0</v>
-      </c>
-      <c r="M93">
-        <v>0</v>
-      </c>
-      <c r="N93" t="s">
+      <c r="J93" s="1">
+        <v>0</v>
+      </c>
+      <c r="K93" s="1">
+        <v>3</v>
+      </c>
+      <c r="L93" s="1">
+        <v>0</v>
+      </c>
+      <c r="M93" s="1">
+        <v>0</v>
+      </c>
+      <c r="N93" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="P93" t="s">
+      <c r="P93" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="94" spans="1:16">
-      <c r="A94" s="1">
+      <c r="A94" s="2">
         <f t="shared" si="6"/>
         <v>100803</v>
       </c>
-      <c r="B94" s="1">
+      <c r="B94" s="2">
         <f t="shared" si="9"/>
         <v>1008</v>
       </c>
-      <c r="C94">
-        <v>3</v>
-      </c>
-      <c r="D94" t="s">
+      <c r="C94" s="1">
+        <v>3</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E94" t="s">
-        <v>74</v>
-      </c>
-      <c r="F94" t="s">
+      <c r="E94" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F94" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G94" t="s">
+      <c r="G94" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="H94">
-        <v>0</v>
-      </c>
-      <c r="I94">
+      <c r="H94" s="1">
+        <v>0</v>
+      </c>
+      <c r="I94" s="1">
         <v>4</v>
       </c>
-      <c r="J94">
-        <v>0</v>
-      </c>
-      <c r="K94">
-        <v>3</v>
-      </c>
-      <c r="L94">
-        <v>0</v>
-      </c>
-      <c r="M94">
-        <v>0</v>
-      </c>
-      <c r="N94" t="s">
+      <c r="J94" s="1">
+        <v>0</v>
+      </c>
+      <c r="K94" s="1">
+        <v>3</v>
+      </c>
+      <c r="L94" s="1">
+        <v>0</v>
+      </c>
+      <c r="M94" s="1">
+        <v>0</v>
+      </c>
+      <c r="N94" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="P94" t="s">
+      <c r="P94" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="95" spans="1:16">
-      <c r="A95" s="1">
+      <c r="A95" s="2">
         <f t="shared" si="6"/>
         <v>100804</v>
       </c>
-      <c r="B95" s="1">
+      <c r="B95" s="2">
         <f t="shared" si="9"/>
         <v>1008</v>
       </c>
-      <c r="C95">
+      <c r="C95" s="1">
         <v>4</v>
       </c>
-      <c r="D95" t="s">
+      <c r="D95" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E95" t="s">
-        <v>74</v>
-      </c>
-      <c r="F95" t="s">
+      <c r="E95" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F95" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G95" t="s">
+      <c r="G95" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="H95">
-        <v>0</v>
-      </c>
-      <c r="I95">
+      <c r="H95" s="1">
+        <v>0</v>
+      </c>
+      <c r="I95" s="1">
         <v>4</v>
       </c>
-      <c r="J95">
-        <v>0</v>
-      </c>
-      <c r="K95">
-        <v>3</v>
-      </c>
-      <c r="L95">
-        <v>0</v>
-      </c>
-      <c r="M95">
-        <v>0</v>
-      </c>
-      <c r="N95" t="s">
+      <c r="J95" s="1">
+        <v>0</v>
+      </c>
+      <c r="K95" s="1">
+        <v>3</v>
+      </c>
+      <c r="L95" s="1">
+        <v>0</v>
+      </c>
+      <c r="M95" s="1">
+        <v>0</v>
+      </c>
+      <c r="N95" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="P95" t="s">
+      <c r="P95" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="96" spans="1:16">
-      <c r="A96" s="1">
+      <c r="A96" s="2">
         <f t="shared" si="6"/>
         <v>100805</v>
       </c>
-      <c r="B96" s="1">
+      <c r="B96" s="2">
         <f t="shared" si="9"/>
         <v>1008</v>
       </c>
-      <c r="C96">
+      <c r="C96" s="1">
         <v>5</v>
       </c>
-      <c r="D96" t="s">
+      <c r="D96" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E96" t="s">
-        <v>74</v>
-      </c>
-      <c r="F96" t="s">
+      <c r="E96" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F96" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G96" t="s">
+      <c r="G96" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="H96">
-        <v>0</v>
-      </c>
-      <c r="I96">
+      <c r="H96" s="1">
+        <v>0</v>
+      </c>
+      <c r="I96" s="1">
         <v>4</v>
       </c>
-      <c r="J96">
-        <v>0</v>
-      </c>
-      <c r="K96">
-        <v>3</v>
-      </c>
-      <c r="L96">
-        <v>0</v>
-      </c>
-      <c r="M96">
-        <v>0</v>
-      </c>
-      <c r="N96" t="s">
+      <c r="J96" s="1">
+        <v>0</v>
+      </c>
+      <c r="K96" s="1">
+        <v>3</v>
+      </c>
+      <c r="L96" s="1">
+        <v>0</v>
+      </c>
+      <c r="M96" s="1">
+        <v>0</v>
+      </c>
+      <c r="N96" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="P96" t="s">
+      <c r="P96" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="97" spans="1:16">
-      <c r="A97" s="1">
+      <c r="A97" s="2">
         <f t="shared" si="6"/>
         <v>100806</v>
       </c>
-      <c r="B97" s="1">
+      <c r="B97" s="2">
         <f t="shared" si="9"/>
         <v>1008</v>
       </c>
-      <c r="C97">
+      <c r="C97" s="1">
         <v>6</v>
       </c>
-      <c r="D97" t="s">
+      <c r="D97" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E97" t="s">
-        <v>74</v>
-      </c>
-      <c r="F97" t="s">
+      <c r="E97" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F97" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G97" t="s">
+      <c r="G97" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="H97">
-        <v>0</v>
-      </c>
-      <c r="I97">
+      <c r="H97" s="1">
+        <v>0</v>
+      </c>
+      <c r="I97" s="1">
         <v>4</v>
       </c>
-      <c r="J97">
-        <v>0</v>
-      </c>
-      <c r="K97">
-        <v>3</v>
-      </c>
-      <c r="L97">
-        <v>0</v>
-      </c>
-      <c r="M97">
-        <v>0</v>
-      </c>
-      <c r="N97" t="s">
+      <c r="J97" s="1">
+        <v>0</v>
+      </c>
+      <c r="K97" s="1">
+        <v>3</v>
+      </c>
+      <c r="L97" s="1">
+        <v>0</v>
+      </c>
+      <c r="M97" s="1">
+        <v>0</v>
+      </c>
+      <c r="N97" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="P97" t="s">
+      <c r="P97" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="98" spans="1:16">
-      <c r="A98" s="1">
+      <c r="A98" s="2">
         <f t="shared" si="6"/>
         <v>100807</v>
       </c>
-      <c r="B98" s="1">
+      <c r="B98" s="2">
         <f t="shared" si="9"/>
         <v>1008</v>
       </c>
-      <c r="C98">
+      <c r="C98" s="1">
         <v>7</v>
       </c>
-      <c r="D98" t="s">
+      <c r="D98" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E98" t="s">
-        <v>74</v>
-      </c>
-      <c r="F98" t="s">
+      <c r="E98" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F98" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G98" t="s">
+      <c r="G98" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="H98">
-        <v>0</v>
-      </c>
-      <c r="I98">
+      <c r="H98" s="1">
+        <v>0</v>
+      </c>
+      <c r="I98" s="1">
         <v>4</v>
       </c>
-      <c r="J98">
-        <v>0</v>
-      </c>
-      <c r="K98">
-        <v>3</v>
-      </c>
-      <c r="L98">
-        <v>0</v>
-      </c>
-      <c r="M98">
-        <v>0</v>
-      </c>
-      <c r="N98" t="s">
+      <c r="J98" s="1">
+        <v>0</v>
+      </c>
+      <c r="K98" s="1">
+        <v>3</v>
+      </c>
+      <c r="L98" s="1">
+        <v>0</v>
+      </c>
+      <c r="M98" s="1">
+        <v>0</v>
+      </c>
+      <c r="N98" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="P98" t="s">
+      <c r="P98" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="99" spans="1:16">
-      <c r="A99" s="1">
+      <c r="A99" s="2">
         <f t="shared" si="6"/>
         <v>100808</v>
       </c>
-      <c r="B99" s="1">
+      <c r="B99" s="2">
         <f t="shared" si="9"/>
         <v>1008</v>
       </c>
-      <c r="C99">
+      <c r="C99" s="1">
         <v>8</v>
       </c>
-      <c r="D99" t="s">
+      <c r="D99" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E99" t="s">
-        <v>74</v>
-      </c>
-      <c r="F99" t="s">
+      <c r="E99" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F99" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G99" t="s">
+      <c r="G99" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="H99">
-        <v>0</v>
-      </c>
-      <c r="I99">
+      <c r="H99" s="1">
+        <v>0</v>
+      </c>
+      <c r="I99" s="1">
         <v>4</v>
       </c>
-      <c r="J99">
-        <v>0</v>
-      </c>
-      <c r="K99">
-        <v>3</v>
-      </c>
-      <c r="L99">
-        <v>0</v>
-      </c>
-      <c r="M99">
-        <v>0</v>
-      </c>
-      <c r="N99" t="s">
+      <c r="J99" s="1">
+        <v>0</v>
+      </c>
+      <c r="K99" s="1">
+        <v>3</v>
+      </c>
+      <c r="L99" s="1">
+        <v>0</v>
+      </c>
+      <c r="M99" s="1">
+        <v>0</v>
+      </c>
+      <c r="N99" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="P99" t="s">
+      <c r="P99" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="100" spans="1:16">
-      <c r="A100" s="1">
+      <c r="A100" s="2">
         <f t="shared" si="6"/>
         <v>100809</v>
       </c>
-      <c r="B100" s="1">
+      <c r="B100" s="2">
         <f t="shared" si="9"/>
         <v>1008</v>
       </c>
-      <c r="C100">
+      <c r="C100" s="1">
         <v>9</v>
       </c>
-      <c r="D100" t="s">
+      <c r="D100" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E100" t="s">
-        <v>74</v>
-      </c>
-      <c r="F100" t="s">
+      <c r="E100" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F100" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G100" t="s">
+      <c r="G100" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="H100">
-        <v>0</v>
-      </c>
-      <c r="I100">
+      <c r="H100" s="1">
+        <v>0</v>
+      </c>
+      <c r="I100" s="1">
         <v>4</v>
       </c>
-      <c r="J100">
-        <v>0</v>
-      </c>
-      <c r="K100">
-        <v>3</v>
-      </c>
-      <c r="L100">
-        <v>0</v>
-      </c>
-      <c r="M100">
-        <v>0</v>
-      </c>
-      <c r="N100" t="s">
+      <c r="J100" s="1">
+        <v>0</v>
+      </c>
+      <c r="K100" s="1">
+        <v>3</v>
+      </c>
+      <c r="L100" s="1">
+        <v>0</v>
+      </c>
+      <c r="M100" s="1">
+        <v>0</v>
+      </c>
+      <c r="N100" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="P100" t="s">
+      <c r="P100" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="101" spans="1:16">
-      <c r="A101" s="1">
+      <c r="A101" s="2">
         <f t="shared" si="6"/>
         <v>100810</v>
       </c>
-      <c r="B101" s="1">
+      <c r="B101" s="2">
         <f t="shared" si="9"/>
         <v>1008</v>
       </c>
-      <c r="C101">
+      <c r="C101" s="1">
         <v>10</v>
       </c>
-      <c r="D101" t="s">
+      <c r="D101" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E101" t="s">
-        <v>74</v>
-      </c>
-      <c r="F101" t="s">
+      <c r="E101" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F101" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G101" t="s">
+      <c r="G101" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="H101">
-        <v>0</v>
-      </c>
-      <c r="I101">
+      <c r="H101" s="1">
+        <v>0</v>
+      </c>
+      <c r="I101" s="1">
         <v>4</v>
       </c>
-      <c r="J101">
-        <v>0</v>
-      </c>
-      <c r="K101">
-        <v>3</v>
-      </c>
-      <c r="L101">
-        <v>0</v>
-      </c>
-      <c r="M101">
-        <v>0</v>
-      </c>
-      <c r="N101" t="s">
+      <c r="J101" s="1">
+        <v>0</v>
+      </c>
+      <c r="K101" s="1">
+        <v>3</v>
+      </c>
+      <c r="L101" s="1">
+        <v>0</v>
+      </c>
+      <c r="M101" s="1">
+        <v>0</v>
+      </c>
+      <c r="N101" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="P101" t="s">
-        <v>74</v>
+      <c r="P101" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16">
+      <c r="A102" s="2">
+        <f t="shared" si="6"/>
+        <v>4001001</v>
+      </c>
+      <c r="B102" s="1">
+        <v>40010</v>
+      </c>
+      <c r="C102" s="1">
+        <v>1</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H102" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I102" s="1">
+        <v>1</v>
+      </c>
+      <c r="J102" s="1">
+        <v>12</v>
+      </c>
+      <c r="K102" s="1">
+        <v>0</v>
+      </c>
+      <c r="L102" s="1">
+        <v>101</v>
+      </c>
+      <c r="M102" s="1">
+        <v>30</v>
+      </c>
+      <c r="P102" s="1">
+        <v>203005</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16">
+      <c r="A103" s="2">
+        <f t="shared" si="6"/>
+        <v>4001002</v>
+      </c>
+      <c r="B103" s="1">
+        <v>40010</v>
+      </c>
+      <c r="C103" s="1">
+        <v>2</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H103" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I103" s="1">
+        <v>1</v>
+      </c>
+      <c r="J103" s="1">
+        <v>12</v>
+      </c>
+      <c r="K103" s="1">
+        <v>0</v>
+      </c>
+      <c r="L103" s="1">
+        <v>101</v>
+      </c>
+      <c r="M103" s="1">
+        <v>30</v>
+      </c>
+      <c r="P103" s="1">
+        <v>203010</v>
+      </c>
+    </row>
+    <row r="104" ht="27" spans="1:16">
+      <c r="A104" s="2">
+        <f t="shared" si="6"/>
+        <v>4001003</v>
+      </c>
+      <c r="B104" s="1">
+        <v>40010</v>
+      </c>
+      <c r="C104" s="1">
+        <v>3</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H104" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I104" s="1">
+        <v>1</v>
+      </c>
+      <c r="J104" s="1">
+        <v>12</v>
+      </c>
+      <c r="K104" s="1">
+        <v>0</v>
+      </c>
+      <c r="L104" s="1">
+        <v>101</v>
+      </c>
+      <c r="M104" s="1">
+        <v>30</v>
+      </c>
+      <c r="P104" s="1" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
